--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -445,10 +445,674 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>큐텐상품번호</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>상점ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>상품명(원본)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>한글검증명칭</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>가격(엔)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>옵션있음</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>카테고리코드</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1213065508</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>deesse1128</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>【2026新作】ダルバ エアフィット ブルー トーンアップUVパウダー 5.5g SPF UVケア 毛穴カバー テカリケア ヴィーガン</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213065508</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1184719855</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>deesse1128</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[新作]ローズマリー PDRN クーリング 脱毛シャンプー 400ml #EGF 頭皮鎮静 脱毛ケア/ローズマリー PDRN クールスカルプシャンプー/根元からふんわりボリュームケア</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184719855</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1211478917</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>deesse1128</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>【26年新リニューアル】ダルバ ヴィーガン ヘアパフュームセラム 100ml ヘアミスト 保湿 ダメージケア 韓国コスメプロフェッショナルリペアリングヘアパフュームセラム</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211478917</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1211980957</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>deesse1128</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>【NEW】オウズナリー ビタ3 オーロラミスト 60ml メイクキープ ツヤミスト 保湿 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>オーズナリー</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211980957</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1178226810</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rarimarket</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[NEW]PDRNピンクコラーゲンボリュームマルチバーム 10g/PDRN Pink Collagen Volume Multi Balm</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>4190</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1178226810</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1178226702</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rarimarket</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[1+1]ティーツリーシカポア鼻パック 5枚</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1178226702</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1178226617</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rarimarket</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>オールデイ メイクアップ フィクサー 75ml/SO.NATURAL/FIXX/ALL DAY/MAKE UP SETTING</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ソーナチュラル</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1178226617</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1206008325</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DreamWish</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ペプチドショット2X 弾力アンプル 30ml（ハリ感ケア／保湿／弾力サポート美容液）</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>アンプルエヌ</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2122</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206008325</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1206008294</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DreamWish</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ウォーターフィット リカバー BBクリーム 30ml #SPF40 PA+++ #保湿密着</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>セルフュージョンC</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2927</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206008294</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1174866024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>247GOODLUCK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>グレーズ ヘアパフュームオイル 45ml</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ケラスターゼ</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>7405</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1174866024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1206005784</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>busanjin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ローズオブセッション ティント 24種（グロウ/マット）</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>フィー</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1897</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206005784</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1162170897</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>berrymuch</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[25SS/New] PDRN ヒアルロン酸 カプセル100 セラムマスク 10枚入</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2640</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1162170897</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1205905275</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>berrymuch</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>アトバリア365 カプセルトナー 300ml #高密度セラミドカプセル #PHA #弱酸性 #26年5月発売</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AESTURA</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3531</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205905275</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1204558349</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>siriya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>リポソームバブルブースター 95ml 2種（コラーゲン／キャビア PDRN）から1つ選択</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Biodance</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3498</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204558349</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1203110839</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>siriya</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>イレイザー ショット グリコリック酸ブースター 30ml #皮脂・角質除去</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>アレンシア</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4038</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203110839</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A1"/>
+  <autoFilter ref="A1:J16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1111,8 +1111,910 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1136214702</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JUNSTAR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[シミ/白玉セット] グルタチオングロウアンプル 30ml + ディープ ビタC カプセル クリーム 55ml</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5990</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1136214702</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1190200956</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JUNSTAR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>クリムゾン スカイ(ポリッシュ) 8ml #シャンパンスパークル #イブニングパーティー</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FINGER SUIT</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2624</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190200956</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1194311832</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>JUNSTAR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>レッド イレイジングクリーム 2.0 (リニューアル) 50ml</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2490</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194311832</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1188287748</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JUNSTAR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[大容量]ダーマソルトクリーム120ml</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ABpharm</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>10990</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188287748</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1176547134</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JUNSTAR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ポメロ(ポリッシュ) 8ml #シナモンラテ #ピーチオレンジグリッター</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FINGER SUIT</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2090</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1176547134</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1209979406</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>onnicosme</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>【正規品】ハンーユル 幼いヨモギ 皮脂吸着 ヨモギ餅パックフォーム 120ml, 1個</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ハンユル</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3450</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209979406</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1204386062</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>onnicosme</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>【正規品】朝鮮の美女 人参アイクリーム 30ml（ビタミンA レチナール リポソーム）</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2890</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204386062</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1203715344</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>onnicosme</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>【正規品】 フォア パーフェクティング コラーゲン ペプチド クリーム 50ml</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Biodance</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4190</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203715344</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1202714464</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>onnicosme</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>【正規品】 マデカーメラキャプチャーアンプルパッド60枚x2個</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>センテリアン24</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3890</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202714464</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1200863342</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DEdge</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[テミンのフォトカード100%プレゼント] マスターズ アイシー ジェリー サンスティック 14g</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AHC</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3459</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200863342</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1209710276</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DEdge</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[26SS/New]パフュームヘアシャンプー 530ml（+100ml） #Angel muguet発売</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>La'dor</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>4344</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209710276</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1202412626</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DEdge</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>パーフェクトフレッシュ メンズ 男性用洗浄剤 150ml</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ベントン</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202412626</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1196939883</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DEdge</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>レチナール アイセラム リフティングローラー 15ml #カフェイン #バクチオール #アンチエイジングアプリケーター</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>アビブ</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5063</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1196939883</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1146350889</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>seoulselectstore</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>トコフェロールビタミンEオイル原液10ml×6本 高濃度美容オイル 保湿ケア 大容量お得セット</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>マルグルダム</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>5870</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1146350889</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1134579258</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>seoulselectstore</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>【New】グロウターンエクソソームデュアルラッシュセラム まつ毛美容液 眉毛 育毛 韓国コスメ 24時間ケア エクソソーム 二重 まつ毛ケア 長くなる</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>lily eve</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1134579258</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1135156427</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>allkbeauty</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[ブラックヘッドクレンジングセット]ゼロポアブラックヘッドディープクレンジングオイル 205ml+ゼロフォームクレンザー 120g+ブラックヘッド毛穴ブラシプレゼン/zero pore</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1135156427</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1193966544</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>jandb</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Celladix トリプルレチノールウォッシュピール 30ml/Triple Retinol Wash Peel/3x</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>セラディックス</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193966544</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1116658196</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>jandb</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PDRN ピーディーアールエヌ ヒアルロン酸カプセル 100セラム 30ml+リフィル30ml</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1116658196</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1104859818</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>jandb</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[ビタ3種セット] ビタミストセラム8％70ml＋ビタトーニングカプセルセラム100ml＋ビタトーニングセラムローション100ml／カプセルクリーム55g</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>9190</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1104859818</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1210644526</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>trailblue2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[26SS/New]レチナルペプチドセラム 30ml #ナノレチナール #ボツリヌスペプチド #9種ペプチド</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>VTコスメティックス</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>4190</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210644526</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1203041226</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>trailblue2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>(ポケモンエディション)体臭ソリューション デオドラント ボディウォッシュ 720ml 2種から1つ選択</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>46CM</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2490</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203041226</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1187774792</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>trailblue2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[25SS/新作](+セボムミスト贈呈)フレッシュセボム ヘアマスカラ</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>narka</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2249</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1187774792</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J16"/>
+  <autoFilter ref="A1:J38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2013,8 +2013,418 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1209320737</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FaceiD</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[2PACK] クリーンイットゼロ 抹茶クレンジングバーム 100ml</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>バニラコ</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>4555</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209320737</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1201575924</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FaceiD</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[26SS/New]ピーチフェア ビーガン トーンアップ カプセルサンスクリーン 50ml #SPF50+ PA++++ #グルタチオン #ナイアシンアミド</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ホイップド</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3353</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1201575924</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1202081690</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>lily_cosme</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>【2026年新発売・国内正規品】POLA ポーラ ホワイトショット クリアスキンローション150ml 無香料 化粧水 医薬部外品</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ポーラ</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>8922</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202081690</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1076069559</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>lily_cosme</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>【選べる香り ショッパー付き 】SHIRO シロ サボン ホワイトリリー ボディコロン 100ml 箱なし フレグランス</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SHIRO</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3411</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1076069559</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1146297098</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LANLANCOSME</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>POLA ポーラ ホワイトショット セラムUV WSセラムUV 45g SPF50+ PA++++ 日焼け止め</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ポーラ</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>6269</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1146297098</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1138399165</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LANLANCOSME</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>McCoy マッコイ ENEW アクティブバーン 460mg×180粒 サプリメント ACTIVE BURN 栄養機能食品 Lカルニチン αリポ酸</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>mccoy</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>13166</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1138399165</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1110755534</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LANLANCOSME</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MT メタトロン化粧品 コントア エマルジョン 乳液 50ml</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>MTメタトロン</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>5303</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1110755534</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1093334597</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>tokitomecosme</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CHRISTINA クリスティーナ アンストレス トータルセレニティセラム 30mL 美容液 セラム スキンケア</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CHRISTINA</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>10686</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1093334597</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1204362475</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>cloverstore</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>アルティム8 スブリム ビューティ クレンジング オイルn 150mL スキンケア 洗顔 メイク落とし[ギフトラッピング対応]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>シュウウエムラ</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>4928</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204362475</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1058092233</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Megumi7</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[組合せ自由][2個セット]メロウ カーム リラックス ディープナイトリペアシャンプー トリートメント ボディソープ 詰め替え用 レフィル 夜間美容 保湿[ギフトラッピング対応]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>YOLU</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1972</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1058092233</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J38"/>
+  <autoFilter ref="A1:J48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2423,8 +2423,254 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1151138777</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>molimoli</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[2個セット] ハイドロミスト メロウ メルティ リポアオイル ハイドロミルク 本体 詰替[7種類から選べる][ギフトラッピング対応]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>plus eau</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3144</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7</v>
+      </c>
+      <c r="H49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1151138777</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1111082750</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>kosumesebun</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[5枚セット]フェイシャル トリートメント マスク 1枚 (箱なし) お試し[ギフトラッピング対応]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SK-Ⅱ</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>6074</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1111082750</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1197005233</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>itsumi-jp</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[組合せ自由][2個セット]モイスト スムース シャンプートリートメント 詰め替え用 本体 ヘアケア ツヤ髪 摩擦 [ギフトラッピング対応]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>メルト</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2898</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197005233</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1192672600</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>luckybravo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[3個セット]B.A ウォッシュ 7 ミニサイズ 9g 洗顔クリーム お試しサイズ 旅行 トラベル 小分け 基礎化粧品 ハリうるおい [ギフトラッピング対応]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ポーラ</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2582</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1192672600</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1031350344</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>yotubaec</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[箱なし] [5種類から選べる] ビューティクリア パウダーウォッシュ 0.4g×32個 酵素洗顔パウダー 毛穴 皮脂[ギフトラッピング対応]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>スイサイ</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1826</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1031350344</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1136468573</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>yotubaec</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NA エッセンスN 50mL 美容液 ナイアシンアミド 浸透 乾燥 毛穴 うるおい スキンケア[ギフトラッピング対応]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>アンレーベルラボ</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2197</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1136468573</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J48"/>
+  <autoFilter ref="A1:J54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2669,8 +2669,787 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1122759019</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>leekorea</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>【大容量】リフィル/本品/クリームスキン ローション 化粧水 ローション しっとり さっぱり うるおい 乾燥肌 混合肌 オイリー肌 韓国 韓国コスメ アモーレパシフィック</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ラネージュ</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1122759019</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1199397191</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>glovey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>マスクフィット メイクキープ ミスト 密着キープ 崩れ防止 レッド 80ml</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ティルティル</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199397191</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1198611443</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>glovey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>マダガスカルセンテラアンプル 100ml</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>3130</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198611443</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1197582691</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>glovey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ナイアシンアミド 10 トラネキサミック酸 4 ダークスポット コレクティング セラム 30ml</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4</v>
+      </c>
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197582691</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1208272698</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>glovey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>レッドイレイジングクリーム 2.0 50ml</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208272698</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1208271013</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>glovey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>コラーゲンジェリークリーム 110ml</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>3930</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208271013</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1209088264</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GloryofSeoul</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Centella Poremizing Clear Ampoule Pad , 60 Pads</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>2112</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209088264</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1190423964</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GloryofSeoul</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Cream 35ml</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>celimax</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4</v>
+      </c>
+      <c r="H62" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190423964</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1094393233</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GYUWOO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>THEビタAレチナールショットタイトニングブースター 15ml</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>celimax</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1094393233</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1119604228</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>GYUWOO</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>シカ消しゴムパッド 60枚</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>celimax</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1119604228</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1119598747</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>GYUWOO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ノニアクネバブルクレンザー 155ml</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>celimax</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1119598747</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1183043654</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PICNICKOREA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1025独島クレンザー 弱酸性 洗顔フォーム 海洋深層水 ミネラル配合 150ml</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1183043654</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1077111817</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PICNICKOREA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>オリジナル カタツムリ マスクパック 10枚セット / 保湿 弾力 潤い 肌荒れ ケア スキンケア 毎日パック 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ジャミンギョン</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1077111817</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1210090249</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PICNICKOREA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ビタミンCブースターショット 1+1セット フェイス&amp;amp;アイクリーム くすみ・色素沈着ケア グルタチオン配合 30ml×2本</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>アレンシア</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210090249</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1173421783</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MEWA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>プロ ダメージヘア ヘアブラシ （4種選択1）</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>タングルエンジェル</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2990</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1173421783</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1165210718</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MEWA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>レチノール 1% スクアランセラム 30ml</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ジオーディナリー</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1165210718</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1198551506</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>nekohime</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ムード ペブル ハードナー (コーティングミルク/ピーチガード/ナッティコア/ベリーバリア)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ロムアンド</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1512</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198551506</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1161381618</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>nekohime</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>サンマデカクリーム 50ml</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>センテリアン24</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1654</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="b">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1161381618</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1204176921</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>nekohime</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>[medicube] ブラックヘッド毛穴ブラシ</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1690</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="b">
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204176921</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J54"/>
+  <autoFilter ref="A1:J73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3448,8 +3448,49 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1204430506</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>mongdies_jp</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>【ギフトBOX】アウアスキン ハンドクリーム＋リップバーム 2点セット フローラルモスクの香り 誕生日 出産祝い プレゼント 女性 手荒れ 唇荒れ 乾燥 敏感 高保湿ケア 手のシワ パフューム　韓国</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>モンディエス</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204430506</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J73"/>
+  <autoFilter ref="A1:J74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3489,8 +3489,377 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1205506863</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ohype</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>【全商品よりどり】 ボンディングケラチンフォームトリートメント200ml / ボンディングアルファケラチンヘアパック 260g / Nude Musk / Green Zest / ダメージケア</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ohype</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>4350</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="b">
+        <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205506863</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1204360681</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ohype</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>【公式】 ボンディングアルファケラチンヘアパック 260g / Nude Musk / ジェラートヘアパック / マーブルセラピー / ダメージケア / サロンクリニック / 髪の絡まりを改善</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ohype</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204360681</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1203329038</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>beauty69</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>【新作】スムース＆ピュア アイス クーリング デオ スプレー 150ml 2種</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>アリウル</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1676</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203329038</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1204368140</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CosmeticsNo1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ラディアンソーム100マイクロフルーダイザトナー＋エッセンス</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204368140</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1212645182</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CosmeticsNo1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>[1+1+1]ボルフィリン 20% アンプルスティック 10ml x 3EA</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Derma Factory</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212645182</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1212154060</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CosmeticsNo1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>[1+1+1]トラネキサム酸6%クリーム, 30ml x 3EA</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Derma Factory</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212154060</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1212147421</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CosmeticsNo1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>[1+1]トラネキサム酸6%クリーム, 30ml x 2EA</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Derma Factory</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212147421</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1199006617</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Jurian</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>アゼライン酸16BBカーミングセラム, 30ml</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>2578</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199006617</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1199701690</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Jurian</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>カーミング バランスジェル 100ml / 水分バランス 調節</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>4735</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="b">
+        <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199701690</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J74"/>
+  <autoFilter ref="A1:J83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3858,8 +3858,582 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1171638753</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>UKB</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ソウル 1988 セラム: レチナール リポソーム 2% + ブラックジンセン 30ml</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>K-SECRET</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171638753</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1168676299</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>UKB</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>モイスチャー·レイヤ·サン·プロテクター50ml SPF50+ PA++++</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>3995</v>
+      </c>
+      <c r="G85" t="n">
+        <v>9</v>
+      </c>
+      <c r="H85" t="b">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1168676299</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1187961763</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>heyyou</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>[2026] NEW 最低特典カーミング バランスジェル-保湿 / 鎮静 100ml(1+1)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>10057</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3</v>
+      </c>
+      <c r="H86" t="b">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1187961763</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1174936338</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>heyyou</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>プリジュビネーション ファーミングバクチオールセラム[童顔弾力セラム] 50ml</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Dr.Jart+</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>6902</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1174936338</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1208171928</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>heyyou</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>[2026BEST] ザマトロジー 2種 セット-光彩 / 弾力(ブースター130ml+セラム45ml)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>13046</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208171928</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1210644303</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>on_j4052</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>【NEW】SW19 ヘアパフュームミスト 75ml 5pm 8am 2種から選べる1種 ヘアミスト ヘアフレグランス 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SW19</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>5490</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="b">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210644303</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1210988490</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>KBeautyMarket</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>[正規品] SET VQM Phytocin VIBANQM LOTION 30ml + フィニッシュローション20ml</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>CONAPIDIL</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>11780</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="b">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210988490</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1212008071</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>KBeautyMarket</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>[正規品] ナチュラル毛穴カバー乳液 韓国正規品</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>オブジェ</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>3070</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="b">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212008071</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1211131806</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KBeautyMarket</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>[公式販売店] ザマトロジー 2種セット[ブースター+セラム]/韓国化粧品</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>11970</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="b">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211131806</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1211312549</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>KBeautyMarket</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>[公式販売店] 【1+1】 低刺激ディープクレンジング モイスチャー クレンジングオイル 145ml</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>7790</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="b">
+        <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211312549</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1211131359</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>KBeautyMarket</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>[公式販売店] ICD 3種 ラジアンソーム100トナー/クリーム/エッセンス</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>29990</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="b">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211131359</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1177131836</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>koreahubshop</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ドクターヘディソンピュア100％ビタミンCパウダー50gアンプルトナービタケア</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Dr. Hedison</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>4560</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="b">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1177131836</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1189937314</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>koreahubshop</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>アノブ ディープ ダメージ リペア シャンプー 1 + 1 ダブルセット 500ml+500ml</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>UNOVE</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>4840</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="b">
+        <v>0</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189937314</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1189781351</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>YOUSTUDIO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ブライタミン V7トーニング ライトクリーム 50ml</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Dr.Jart+</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>5299</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="b">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189781351</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J83"/>
+  <autoFilter ref="A1:J97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4432,8 +4432,336 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1196020481</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NDY</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ツーフェイス オイルミスト 50ml 1個 基礎化粧品 保湿 潤い 艶肌 油水分バランス [並行輸入品]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>インセルダーム</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>4980</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" t="b">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1196020481</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1170033513</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>LuckyLucy</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>プレミアムペプチド ナイター 1500ショット ネックパッチ1.0,1枚 /3枚購入ごとに ペプチドトックス ボア/ 体系的管理/一日一枚の習慣で荒れていたネックラインを滑らかに~</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>メディピール</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="b">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1170033513</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1194273240</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LuckyLucy</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>プレミアムペプチド ナイター 1500ショット ネックパッチ1.0_1セット(4枚） /1か月集中管理/ 体系的管理/一日一枚の習慣で荒れていたネックラインを滑らかに~</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>メディピール</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>4580</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="b">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194273240</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1193753404</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>LuckyLucy</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>プレミアムペプチド ナイテ 1000 ショート ネックスティック20g+Collagen Naite Thread Neck Cream1.5ml*2ea</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>メディピール</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>4680</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="b">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193753404</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1193262729</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>YoiYoii</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>3デイズ レイヤー アンプル 55ml 美容液スキンケア,韓国スキンケア, 人気コスメ, 保湿</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>REVCELL</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>5848</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2</v>
+      </c>
+      <c r="H102" t="b">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193262729</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1207093725</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>YoiYoii</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CPR トリプルシナジーリンクルケアセラム 30ml+30ml 韓国コスメ, スキンケア,レチナール 美容液,コラーゲンセラム</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>THOME</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>12833</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="b">
+        <v>0</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207093725</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1200649177</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>cosmenana</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ululis ウルリス プレミアム ウォーターコンク ブラックセラム ヘアオイル 100ml 黒[3559] 宅配無料</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ululis</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="b">
+        <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200649177</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1171444773</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>lument</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>【正規品 / 140ml】赤あずき クレイパック / あずきパック 毛穴 黒ずみ 角質 くすみ 洗い流す 韓国コスメ 韓国伝統成分×毛穴集中ケア</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H105" t="b">
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171444773</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4760,8 +4760,664 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1113959443</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>deos_jp</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>コラーゲン ロールオン アイクリーム 30ml 韓国コスメ 目元ケア ハリ ツヤ 保湿 ステンレス製3連ローラー 目元美容液</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>プリティースキン</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3</v>
+      </c>
+      <c r="H106" t="b">
+        <v>0</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1113959443</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1179879084</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>deos_jp</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ペプチド PDRN セラムミスト 150ml2％ローズ由来PDRN×10種ペプチドうるおいとハリを同時ケアツボクサ・セラミドNP配合乾燥対策フェイシャルミスト</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>プリティースキン</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="b">
+        <v>0</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179879084</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1158581451</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>deos_jp</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>8種ヒアルロン酸 &amp;amp; ビタミン TECA クリーム (50ml) 水分爆弾 高保湿 鎮静ケア</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>プリティースキン</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>3270</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="b">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1158581451</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1210848436</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SARAHGLO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>FRANZ ネイキッドスポットパッチ デュオ EARLY &amp;amp; DARK 72枚入り</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>FRANZ</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>3552</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="b">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210848436</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1157585444</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>JnGCommerce</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>トータルソリューション 24K ゴールドスネイル クレンジングフォーム 150ml</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>プリティースキン</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1780</v>
+      </c>
+      <c r="G110" t="n">
+        <v>5</v>
+      </c>
+      <c r="H110" t="b">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1157585444</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1206727074</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>JnGCommerce</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>シカエクソソーム 保湿クリーム 60ml 鎮静 敏感肌 肌荒れケア 水分クリーム 韓国コスメ 低刺激</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>プリティースキン</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="b">
+        <v>0</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206727074</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1193888835</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>JnGCommerce</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PDRN TX1 パーフェクトフィット リジュアル 幹細胞クリーム 30g/ローズ PDRN 21%配合 植物性 水分クリーム/キメケア 弾力 保湿/韓国コスメ (敏感肌/乾燥肌)/次世代スキンケア</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>プリティースキン</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G112" t="n">
+        <v>3</v>
+      </c>
+      <c r="H112" t="b">
+        <v>0</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193888835</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1180144570</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>yeppun</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PDRN トナー250ml1個</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>VTコスメティックス</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>3230</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="b">
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180144570</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1202055978</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>yeppun</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>UVクリーム SPF50+ PA ++++ 敏感肌向けトーンアップ韓国コスメの人気日焼け止め</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AESTURA</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>4370</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="b">
+        <v>0</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202055978</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1174315936</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>yeppun</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>1. マデカラボ マスク 10枚×2箱（リンクル リバイタライズ）</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>センテリアン24</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="b">
+        <v>0</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1174315936</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1183743968</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>zz6o6</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>パーフェクト9 インテンシブ スキンケアセット 化粧水 乳液 クリーム セット スキンケア 保湿 セット 保湿</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>イニスフリー</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>5253</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="b">
+        <v>0</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1183743968</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1177458353</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>zz6o6</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>コジサン ソープ 65g×3個 フィリピン製 ナチュラル オレンジ石鹸 ギフトにもおすすめ</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>こじえさん</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>2232</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="b">
+        <v>0</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1177458353</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1189430591</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>hanajini</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ウォータフルトーンアップサンクリーム[ピンク], 50ml</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G118" t="n">
+        <v>5</v>
+      </c>
+      <c r="H118" t="b">
+        <v>0</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189430591</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1198793023</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>hanajini</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>グリーンディープ ポア クレンジングバーム,100mL 1+1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ドクタージー</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G119" t="n">
+        <v>7</v>
+      </c>
+      <c r="H119" t="b">
+        <v>0</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198793023</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1198672888</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>hanajini</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PDRN ブースター ジェル 300mL</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="b">
+        <v>0</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198672888</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1189433592</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>hanajini</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ダブルセラム オールインワン マルチバーム 10g</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" t="b">
+        <v>0</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189433592</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J105"/>
+  <autoFilter ref="A1:J121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$138</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5416,8 +5416,705 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1209471569</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>khy8569</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>プルブア ヒノキレザー オードパルファム 30ml</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>pleuvoir</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>4600</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="b">
+        <v>0</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209471569</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1200469480</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>khy8569</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>シャドーパレット02ローズペタル데이지크 섀도우 팔레트 02로즈페탈</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>デイジーク</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="b">
+        <v>0</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200469480</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>960305321</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>easymall</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ボディスクラブプレステージセラピーエディション180gx4個</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>プル</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>4352</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="b">
+        <v>0</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=960305321</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>960305004</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>easymall</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ダフトアンドドフト パフュームド ボディローション エンジェルコットン 2個 300ml</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ダフト&amp;amp;ドフト</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>3114</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="b">
+        <v>0</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=960305004</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1169665636</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>eightpointone</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ナンバーMノーダウトコラーゲンリフティングクリーム50gホワイトニングシワ改善機能化粧品</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>MEDI SECTION NO.M</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>2885</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="b">
+        <v>0</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169665636</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1213011435</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>eightpointone</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>アクセンダ ルティナー 15ml スリープクリーム スリープバーム + トラベルサイズ ミニ歯磨き粉 セット</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>aXENDA</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>5462</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="b">
+        <v>0</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213011435</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1210202611</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>eightpointone</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>リバイブ セラピー NF アンプル / 30ml / PDRN アンプルデクスパンテノールビタミンB5</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>SKIN9HARI</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>3698</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="b">
+        <v>0</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210202611</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1193801185</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>cosmetch</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>【1点までメール便選択可】 レプリカ ウェン ザ レイン ストップス EDT 10ml SP (香水)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>メゾンマルジェラ</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>2920</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="b">
+        <v>0</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193801185</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1161562524</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>cosmetch</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>プロディジュー フローラル オイル 100ml （全身オイル）</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ニュクス</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>3110</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3</v>
+      </c>
+      <c r="H130" t="b">
+        <v>0</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1161562524</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1168150897</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>cosmetch</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ジャンヌ ランバン EDP 30ml SP （香水）</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ランバン</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>2770</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="b">
+        <v>0</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1168150897</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1191723236</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>treasurebeauty</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ホワイトティ ジンジャーリリー ボディクリーム 400ml</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>エリザベスアーデン</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>3344</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="b">
+        <v>0</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191723236</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1203745241</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>treasurebeauty</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>スキンコンディショナーエッセンシャル 330ml</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>アルビオン</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>10106</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="b">
+        <v>0</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203745241</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1154890233</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>bettysbeauty</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ロム イデアル インテンス オーデパルファン 100ml</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ゲラン</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>20617</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="b">
+        <v>0</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1154890233</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1123998991</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>bettysbeauty</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>イリシットオーデパルファム 100ml</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ジミーチュウ</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>10654</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="b">
+        <v>0</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1123998991</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1163881732</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>bellcosme</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ロレアル セリエ ブロンディファイアー マスク 500ml</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>LOREAL PARIS</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>5374</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="b">
+        <v>0</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163881732</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1123944887</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>bellcosme</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>グリーンティー ボディローション 500ml</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>エリザベスアーデン</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1679</v>
+      </c>
+      <c r="G137" t="n">
+        <v>7</v>
+      </c>
+      <c r="H137" t="b">
+        <v>0</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1123944887</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1204380898</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>bellcosme</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ニューバーム ソフトムスク 40g</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RETOUCH</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>2809</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="b">
+        <v>0</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204380898</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J121"/>
+  <autoFilter ref="A1:J138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6113,8 +6113,582 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1205911392</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>cosmetictimes</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ザ・モイスチャーリフト ファーミング マスク 3ml ミニサイズ</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ドゥ・ラ・メール</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>2664</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="b">
+        <v>0</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205911392</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1205911401</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>cosmetictimes</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>スキンパワー リニュー クリーム 80g</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>SK-Ⅱ</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>24418</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="b">
+        <v>0</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205911401</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1210143801</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>NATSUKISHOP</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DRX HQダブルブライトE　6g</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>ロート製薬</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="b">
+        <v>0</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210143801</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1196958353</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>NATSUKISHOP</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ユーブロックスプレー 90g　2本セット　SPF50+／PA++++</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>サンソリット</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G142" t="n">
+        <v>7</v>
+      </c>
+      <c r="H142" t="b">
+        <v>0</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1196958353</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1189223064</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>tomimori</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>国内正規品　在庫処分　LIPOSOMEコーセー コスメデコルテ リポソームアドバンストリペアアイセラム 20mL送料無料</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>コスメデコルテ</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>5730</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="b">
+        <v>0</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189223064</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1159500251</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>tomimori</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>送料無料　箱なし　shiro シロ　サボン ボディコロン 正規品</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>SHIRO</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="b">
+        <v>0</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1159500251</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1210924259</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>tomimori</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>アネッサ オールインワン ビューティーパクト 1 10g SPF50+・PA+++ 日焼止め UVケア やや明るめのオークル 化粧持ち UVパクト 化粧下地 つや美肌</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>アネッサ</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>2980</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="b">
+        <v>0</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210924259</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1169403361</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>jncompany</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ダーマUV365バリアハイドロミネラルサンスクリーン, [20ml*2] 40ml</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AESTURA</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3</v>
+      </c>
+      <c r="H146" t="b">
+        <v>0</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169403361</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1169403360</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>jncompany</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>エイシカ365 水分鎮静トナー, [25ml*10] 250ml</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AESTURA</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="b">
+        <v>0</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169403360</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1172627984</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>jncompany</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>レチノールスーパーバウンスセラム, [10ml*3] 30ml</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>アイオペ</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G148" t="n">
+        <v>6</v>
+      </c>
+      <c r="H148" t="b">
+        <v>0</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1172627984</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1169403395</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>jncompany</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>エイシカ365スージングリペアクリーム, [10ml*6] 60ml</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AESTURA</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="b">
+        <v>0</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169403395</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1153736512</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>stellacosme</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>[はりんPICK] セラバリア モイスチャー アクティブトナー 200ml</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>ホリカホリカ</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>3601</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="b">
+        <v>0</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1153736512</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1153736555</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>stellacosme</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>[1+1] メルヘンラップ オリジナル 高周波クリーム 800ml, 2個</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>MARCHEN LAB</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>5530</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="b">
+        <v>0</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1153736555</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1212029919</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>K-CosmeMint</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>3番 うるツヤ発酵トナーパッド 70枚 (透明感・キメ整肌・凸凹肌卒業・肌荒れ・ 赤み鎮静・ほてりケア 毛穴引き締め ゆらぎ肌対策 角質・皮脂オフ 朝の時短・部分パック 敏感肌も安心 韓国コスメ)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>ナンバーズイン</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="b">
+        <v>0</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212029919</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J138"/>
+  <autoFilter ref="A1:J152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6687,8 +6687,582 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1171810163</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>joohoh2</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>モイスチャー サージ インテンス 72 H リピッド-リプレニッシング ハイドレーター 50ml / 75ml [こっくり 潤うリッチ クリーム]</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>クリニーク</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>3744</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="b">
+        <v>0</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171810163</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1207330609</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>joohoh2</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>[メンズ オールインワン 限定企画3種セット] アクアパワー オールインワン 200ml セット ＋クレンザー40ml／オールインワン20ml 付き</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>ビオテルム</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>5292</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="b">
+        <v>0</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207330609</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1157224885</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>beautyonion</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ヨモギ ゼロフィルム クレンジングオイル 200ML</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Orien</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>2520</v>
+      </c>
+      <c r="G155" t="n">
+        <v>6</v>
+      </c>
+      <c r="H155" t="b">
+        <v>0</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1157224885</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1009082270</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>beautyonion</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ポアマイジング フラッシュ アンプル 100ml</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>2087</v>
+      </c>
+      <c r="G156" t="n">
+        <v>4</v>
+      </c>
+      <c r="H156" t="b">
+        <v>0</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1009082270</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1197590797</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>sioris</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>【ゆらぎ肌対策】マイファーストエッセナー100ml 2本J.Y. Parkプロデュース/緑茶エキス/鎮静ブースター/オーガニック認証</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>シオリス</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>7326</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="b">
+        <v>0</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197590797</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1197574204</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>sioris</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>【乾燥対策】【ミスト2本セット】タイムイズランニングアウトミスト100mlユズ果実エキス/オイルイン/べたつかない/保湿/オーガニック認証</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>シオリス</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>5544</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="b">
+        <v>0</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197574204</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1195971817</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>sioris</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>【低刺激ミルククレンジング】クレンズ ミー ソフトリー ミルククレンザー シグニチャー 200ml低pH高保湿/ダブル洗顔不要/弱酸性/乾燥肌</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>シオリス</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>3630</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" t="b">
+        <v>0</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1195971817</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1200863299</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>quvee</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>MAPSI シャマッククリーム 80ml (2+1) / 水分バリア / 保湿クリーム / 肌修復 / 保湿 / 鎮静 / 低分子コラーゲン / 敏感肌用</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>NOTALY</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="b">
+        <v>0</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200863299</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1173591947</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>quvee</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>デコンジェルシートマスクパック（1BOX5枚）熱感/紅調ケア</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>LEBON</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="b">
+        <v>0</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1173591947</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1161937139</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>quvee</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>80ml ベールクリームミスト 霧状噴射 コラーゲンミスト 水光ミストうるおい＋栄養 ミスト噴射+シートマスク贈呈</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>MEDIPAIR</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>5300</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="b">
+        <v>0</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1161937139</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1163288585</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>quvee</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>タミテンゲル 500ml / 鎮静ジェル/水分ジェル/敏感肌/赤みケア/熱感ケア/ホームケア/水分補給/イスジェル</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>NOTALY</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>11500</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="b">
+        <v>0</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163288585</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1159600473</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>meloa</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>モモ70％ナイアシンセラム 30ml 韓国コスメ ナイアシン アミドセラム 保湿 ダークスポットケア シミケア 美容液</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="b">
+        <v>0</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1159600473</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1163660756</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>meloa</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ビーガン イエローミストセラム 100mlツヤ＋うるおい＋鎮静ケア！オイル層×美容液層の2層式ミスト／化粧直しにも／敏感肌OK／ヴィーガン認証</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="b">
+        <v>0</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163660756</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1161540935</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>bathking</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>バイオEXセルペプチドリンクルパーフェクターマスク30gx10枚</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>トニーモリー</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="b">
+        <v>0</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1161540935</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J152"/>
+  <autoFilter ref="A1:J166"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:J182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7261,8 +7261,664 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1097452938</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>VENDERMA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ニキビ・毛穴・皮脂ケア・急な肌トラブル速攻鎮静 レッドカーミング シカ エクソソーム スポットオイル 10ml</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>VENDERMA</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>2310</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="b">
+        <v>0</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1097452938</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1097452926</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>VENDERMA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ゼロ毛穴・スージングブースター・ニキビ・赤み・リファイニング レッドカーミング シカ エクソソーム トナーエッセンス 150ml</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>VENDERMA</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>3850</v>
+      </c>
+      <c r="G168" t="n">
+        <v>5</v>
+      </c>
+      <c r="H168" t="b">
+        <v>0</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1097452926</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1173839691</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>enseoul</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>酵素ピーリングジェル ガラクトミー成分配合 75mL×3個セット</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>manyo</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>4174</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="b">
+        <v>0</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1173839691</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1190324743</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>enseoul</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ゼロ クレンジングバーム ブライトニング 100mL 3本セット</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>バニラコ</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>9248</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="b">
+        <v>0</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190324743</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1169332727</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>enseoul</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>炭酸パウダー洗顔 濃密泡 毛穴ケア しっとり洗い上がり 150mL 2本セット</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>manyo</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>4949</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="b">
+        <v>0</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169332727</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1163294474</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>enseoul</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>韓蘭 保湿化粧水 170mL 2本セット</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>イニスフリー</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>5820</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="b">
+        <v>0</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163294474</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1161207715</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>enseoul</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>しっとり水分保護 5種ヒアルロン酸×緑茶保湿クリーム 50mL x3</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>イニスフリー</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>9631</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="b">
+        <v>0</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1161207715</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1192489006</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>wjcosmetics</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>【公式】【ドクターズコスメ】WJ センテラ センテレスト スーパーシカ ブースター トナーセラム インナードライ改善 白玉 艶肌 ナイアシンアミド 導入美容液</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>WJ COSMETICS</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>2640</v>
+      </c>
+      <c r="G174" t="n">
+        <v>8</v>
+      </c>
+      <c r="H174" t="b">
+        <v>0</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1192489006</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1173918884</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>FlowLounge</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ダヴ クリーミースクラブ ザクロ＆シアバター 298g 【正規品】 ダブ ボディスクラブ ダヴ ボディスクラブ ダブ スクラブ ダブ ボディスクラブ ダヴ&amp;nbsp;ボディスクラブ</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>ダヴ</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="b">
+        <v>0</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1173918884</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1167546317</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>FlowLounge</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>【百貨店正規品】 アンバーバニラボディクリーム 200g (+無料ギフト) Amber Vanilla</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>ローラメルシエ</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>10980</v>
+      </c>
+      <c r="G176" t="n">
+        <v>2</v>
+      </c>
+      <c r="H176" t="b">
+        <v>0</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1167546317</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1212714853</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>winwinlife1</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>薬用スキンコンディショナー エッセンシャル N（化粧水（敏感肌用））330ml 外箱限定デザイン &amp;amp; 専用フェイシャルコットン 10枚付き スキコン ハトムギ 医薬部外品 スキンケア 肌あれ 乾燥</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>アルビオン</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>8851</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="b">
+        <v>0</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212714853</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1200569716</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>winwinlife1</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>フラルネ ブライトファイン ミルク f M or EM（美白乳液）200g 医薬部外品 リニューアル発売 ブライトニング先行乳液 美白有効成分 透明感 クリア 引き締め メラニン シミ ソバカス</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>アルビオン</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>5701</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+      <c r="H178" t="b">
+        <v>0</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200569716</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1170148962</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>winwinlife1</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>フラルネ フルリファイン ミルク f M or EM 200g 乳液 リニューアル発売 先行乳液 最新美容研究の成果 厳選美容成分 角層まで浸透 肌悩み対策 乾燥・肌荒れ防ぐ 毛穴・くすみケア</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>アルビオン</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>5850</v>
+      </c>
+      <c r="G179" t="n">
+        <v>7</v>
+      </c>
+      <c r="H179" t="b">
+        <v>0</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1170148962</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1164248698</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>winwinlife1</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>プロテクター サンシールドex 顔・ボディ用日やけ止め乳液 30ml 肌保護 UVカット 紫外線ケア 汗・水・皮脂・こすれに強い 日中の有害な外的影響対策 空気中のほこりや汚れの付着もブロック 密着</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>イプサ</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>3348</v>
+      </c>
+      <c r="G180" t="n">
+        <v>2</v>
+      </c>
+      <c r="H180" t="b">
+        <v>0</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1164248698</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1128711574</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>tripleem</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>【国内正規品】　モイスト エフフォーリア クレンジングクリーム　180g　発売日2024/9/17</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>イグニス</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>7320</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="b">
+        <v>0</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1128711574</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1107595984</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>tripleem</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>【国内正規品】　モイスト ウォッシュ クリーム 120g</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>イグニス</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="b">
+        <v>0</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1107595984</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J166"/>
+  <autoFilter ref="A1:J182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J182"/>
+  <dimension ref="A1:J191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7917,8 +7917,377 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1159078786</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>FancyCosme</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AQ ブースティング トリートメント ヘアセラム レフィル (ヘア美容液) 200mL</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>コスメデコルテ</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>4750</v>
+      </c>
+      <c r="G183" t="n">
+        <v>9</v>
+      </c>
+      <c r="H183" t="b">
+        <v>0</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1159078786</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1084098376</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>arcom-shop</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ホワイトショット フェイシャルセラム（美容液）25mL</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>ポーラ</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>11900</v>
+      </c>
+      <c r="G184" t="n">
+        <v>5</v>
+      </c>
+      <c r="H184" t="b">
+        <v>0</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1084098376</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1180998751</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>arcom-shop</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>【国内正規品】AQ リペア シャンプー スムース/ボリューム（レフィル・詰め替え用） 500mL　*</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>コスメデコルテ</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="b">
+        <v>0</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180998751</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1178409133</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>arcom-shop</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>国内正規品 ユース パワー エッセンス ローション (化粧水) 150mL 本体</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>コスメデコルテ</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>14850</v>
+      </c>
+      <c r="G186" t="n">
+        <v>3</v>
+      </c>
+      <c r="H186" t="b">
+        <v>0</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1178409133</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1199167354</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>beauty-q</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026.3.16発売 イドラクラリティ ブライトニング シリーズ 薬用 エッセンス ウォーター・トリートメント ソフナー ・クリーム 美白・肌あれ・保湿・毛穴・ニキビ 国内正規品</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>コスメデコルテ</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>5995</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" t="b">
+        <v>0</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199167354</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1193452641</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>beauty-q</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026.1.16発売 ホワイトロジスト クロノジェネシス ブライトニング コンセントレイト・1.8X(1.8倍最高濃度コウジ酸配合) 国内正規品 2つの濃度の美白美容液 徹底的なシミ対策 高い浸透感</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>コスメデコルテ</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>20980</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="b">
+        <v>0</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193452641</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1180608065</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>korea_gudz</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>スキンフィットグラインディングセラムカバーファクト20g2個/ツヤ肌/低刺激/光彩/ツヤ/美肌/ファンデーション/クッション/メイク/韓国コスメ/本品</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>9273</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="b">
+        <v>0</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180608065</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1175428880</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>korea_gudz</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>語星草70スーディングコラーゲンマスク4枚</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>3764</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="b">
+        <v>0</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1175428880</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1188698439</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>MaruCommerce</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ダイブインマスク, 10枚</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>トリデン</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>1820</v>
+      </c>
+      <c r="G191" t="n">
+        <v>7</v>
+      </c>
+      <c r="H191" t="b">
+        <v>0</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188698439</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J182"/>
+  <autoFilter ref="A1:J191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J191"/>
+  <dimension ref="A1:J196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8286,8 +8286,213 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1199430782</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>charmang</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>[NEW]オールデイブラーメイクアップセッティングフィックスミスト75ml/ふんわり密着/メイクキープスプレー</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>ソーナチュラル</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G192" t="n">
+        <v>3</v>
+      </c>
+      <c r="H192" t="b">
+        <v>0</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199430782</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1168915716</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>charmang</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>【パックツール贈呈】プレミアムモデリングマスクパック1kg/石膏パック【10種】</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>LINDSAY</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>2869</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="b">
+        <v>0</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1168915716</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1133707312</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>charmang</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>【1+1】ダイブインセラム,100mL/ヒアルロン酸/水分/セラム</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>トリデン</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>4749</v>
+      </c>
+      <c r="G194" t="n">
+        <v>3</v>
+      </c>
+      <c r="H194" t="b">
+        <v>0</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1133707312</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1198417997</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>BeautyOn1</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ウォーターグロウメイクアップセッティングフィックスミスト, 75ml</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>ソーナチュラル</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>2050</v>
+      </c>
+      <c r="G195" t="n">
+        <v>5</v>
+      </c>
+      <c r="H195" t="b">
+        <v>0</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198417997</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1198416795</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>BeautyOn1</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>オールデイタイトメイクアップセッティングフィックスミスト, 100ml</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>ソーナチュラル</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="b">
+        <v>0</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198416795</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J191"/>
+  <autoFilter ref="A1:J196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J196"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8491,8 +8491,49 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1189986508</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>onsil</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>【韓国限定】スズラン 香水 / ハンド美容液 / ボディミスト (4種)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>SHIRO</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="b">
+        <v>0</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189986508</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J196"/>
+  <autoFilter ref="A1:J197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8532,8 +8532,213 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1114435648</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>bibian</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>マージェンス マルチ コンディショニング ジェル　（120mL）　男性化粧水　 メンズコスメ　【国内正規品】化粧水 父の日 プレゼント</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>ポーラ</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>2580</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="b">
+        <v>0</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1114435648</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1206085394</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>moomoo0852</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>モンダミンハビットプロ 1080ml 3本</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>モンダミン</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>10204</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="b">
+        <v>0</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206085394</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1204837304</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>moomoo0852</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>アリミノ スプリナージュ トリートメント ジェントルモイスト 1000g レフィル</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>スプリナージュ</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>4568</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="b">
+        <v>0</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204837304</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1187979339</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>chamstore</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>サイン システミックオイル × Kurahashi Rei 【ヘア &amp;amp; ボディ &amp;amp; ハンド用オイル】 (120mL)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>ゴールドサイン</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>1652</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="b">
+        <v>0</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1187979339</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1148906379</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>chamstore</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>スターラボコスメティックス STニュート ヘッドスクラブジェルクールシトラス120g</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>ビューティーワールド</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>2366</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="b">
+        <v>0</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1148906379</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J197"/>
+  <autoFilter ref="A1:J202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J202"/>
+  <dimension ref="A1:J203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8737,8 +8737,49 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1204530869</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>odecomart</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>宅配便 WPDRN グロウセラム 30mL 【3個セット】 PDRN ダブル配合 美容液 保湿 ハリ ツヤ 毛穴 小じわ スキンケア ナイアシンアミド パンテノール ヒアルロン酸</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>ereru</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>7217</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="b">
+        <v>0</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204530869</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J202"/>
+  <autoFilter ref="A1:J203"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$208</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J203"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8778,8 +8778,213 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1210141069</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Lifegarden</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>【2本セット】ミルクブライトニング トナー 300mL 透明感 くすみケア 韓国スキンケア</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>メディヒール</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>3980</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="b">
+        <v>0</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210141069</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1085152294</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>fujifilm-h</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ルナメアAC スキンコンディショナー (ノーマルタイプ) 120ml [医薬部外品] アクネケアローション アクネシューター アクネケア 化粧水 ニキビケア ニキビ予防 肌荒れ ノンコメド</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>富士フイルム</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>2684</v>
+      </c>
+      <c r="G205" t="n">
+        <v>2</v>
+      </c>
+      <c r="H205" t="b">
+        <v>0</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1085152294</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1167420421</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>rebion</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>洗顔フォーム レックスロウウォッシュ 120g 洗顔料 泥 毛穴 50代 40代 濃密泡 泥洗顔料 海シルト 毛穴ケア 毛穴汚れ 黒ずみ 角質ケア 無添加 クレイ洗顔 エイジングケア</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>リビオン</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>2190</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="b">
+        <v>0</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1167420421</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1170385647</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>rebion</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>スキンケア3点セット ヒト幹細胞 保湿 エクソソーム ヒト幹細胞培養液 無添加 ハリ エイジングケア 高保湿 敏感肌 乾燥肌 毛穴 保湿美容液 美肌 潤い 乾燥 化粧水 クリーム</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>リビオン</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>12024</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" t="b">
+        <v>0</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1170385647</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>1209049883</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>attenir</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>クレンジング スキンクリア クレンズ オイル 大容量ボトル＆詰め替え用 (ピースフルオレンジの香り) クレンジングオイル メイク落とし 化粧落とし アロマ 毛穴 350ml</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>アテニア</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>3960</v>
+      </c>
+      <c r="G208" t="n">
+        <v>5</v>
+      </c>
+      <c r="H208" t="b">
+        <v>0</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209049883</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J203"/>
+  <autoFilter ref="A1:J208"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$209</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J208"/>
+  <dimension ref="A1:J209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8983,8 +8983,49 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1186954552</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>mixsoonjp</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ヒアルレベ ポアブラーリングクリーム 50ml 美容液 保湿 毛穴</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>ミクスン</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>2086</v>
+      </c>
+      <c r="G209" t="n">
+        <v>6</v>
+      </c>
+      <c r="H209" t="b">
+        <v>0</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1186954552</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J208"/>
+  <autoFilter ref="A1:J209"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$222</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J209"/>
+  <dimension ref="A1:J222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9024,8 +9024,541 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1128247119</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>happytreemall</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>アルティメット マスク タイム リバース 15 ea</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>ニュースキン</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>8333</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="b">
+        <v>0</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1128247119</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1128246013</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>happytreemall</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>アルティメットマスクウォータープール</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>ニュースキン</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>4568</v>
+      </c>
+      <c r="G211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H211" t="b">
+        <v>0</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1128246013</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1144298674</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>DaisyShop</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>CICA 大容量ライン (化粧水・乳液・クリーム)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>VTコスメティックス</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" t="b">
+        <v>0</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1144298674</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1073380168</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>DaisyShop</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>正規品 セルマン5種オリジナル機能性セット(トナー150ml+セラム30ml+クリーム50ml+ビタミンCセラム30ml+ウォッシュパウダー70g)+/関税なし</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>SERMENT</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>38380</v>
+      </c>
+      <c r="G213" t="n">
+        <v>6</v>
+      </c>
+      <c r="H213" t="b">
+        <v>0</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1073380168</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1169406691</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>DaisyShop</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ビタミンC グロートニングアンプル 30ml</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>NEEDLY</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>1879</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="b">
+        <v>0</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1169406691</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1095176920</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>DaisyShop</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>[DEOPROCE] カタツムリ リカバリー クリーム 100g</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>ディオプラス</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G215" t="n">
+        <v>5</v>
+      </c>
+      <c r="H215" t="b">
+        <v>0</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1095176920</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1190243933</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Seouleye</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>濃縮人参 リニューイング クリーム リッチ 10ml</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>雪花秀</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>1999</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="b">
+        <v>0</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190243933</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1210140814</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>keemz</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>【ポムポムプリン限定 &amp;amp;パーツ＆パフプレゼント】 ライティング トーンアップ サンクッション SPF50+ PA++++</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>アッテ</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="b">
+        <v>0</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210140814</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1204729284</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>gosanke</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>【2個セット】 サブリミック ワンダーシールド h 110ml レフィル リフィル 詰替 ヘア トリートメント 洗い流さない プロフェッショナル アウトバス リニューアル</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>資生堂</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>4780</v>
+      </c>
+      <c r="G218" t="n">
+        <v>2</v>
+      </c>
+      <c r="H218" t="b">
+        <v>0</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204729284</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1213447499</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>onliwon</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>【aespaフォトカード特典】サロン10 ペプチドリペア ヘアミルクエッセンス (150ml+50ml) + ヘアブラシ付き</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>ミジャンセン</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>3105</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="b">
+        <v>0</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213447499</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1213108868</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>onliwon</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>【ENHYPENフォトフィルムランダム1種プレゼント】コン サンセラム 50ml + ビフィダ マスクパック 1枚入り</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>ミクスン</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>3798</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="b">
+        <v>0</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213108868</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1151616310</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>onliwon</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>【DAY6 ウォンピル フォトカード付き】 オードパルファム（全2種・1種選択）</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>After blow</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>4806</v>
+      </c>
+      <c r="G221" t="n">
+        <v>4</v>
+      </c>
+      <c r="H221" t="b">
+        <v>0</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1151616310</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>1186310373</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>onliwon</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>【ALD1フォトカード付き】ジンクテカ フィト サンジェル 50ml（+50ml）</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>3303</v>
+      </c>
+      <c r="G222" t="n">
+        <v>8</v>
+      </c>
+      <c r="H222" t="b">
+        <v>0</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1186310373</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J209"/>
+  <autoFilter ref="A1:J222"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$231</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J222"/>
+  <dimension ref="A1:J231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9557,8 +9557,377 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1175037842</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>cosmejitan</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>髭 隠しながら 抑毛 する 美容液 メンズ コンシーラー BBクリーム ニキビ跡 クマ シミ 青髭 消し ファンドメール ノンビアードクリーム</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>cosmejitan</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G223" t="n">
+        <v>7</v>
+      </c>
+      <c r="H223" t="b">
+        <v>0</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1175037842</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1207945805</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>libio</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>PDRN デュアルエッセンス （２本セット）顔・頭皮用ミスト120mL　低刺激設計　ジェンダーフリー</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>libio</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>10692</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" t="b">
+        <v>0</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207945805</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>1207834466</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>libio</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>PDRN デュアルエッセンス 　顔・頭皮用ミスト120mL　低刺激設計　ジェンダーフリー</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>libio</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>5940</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="b">
+        <v>0</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207834466</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1191891962</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>toun28_official</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>【公式】【NEW】オードパフューム ハンドクリーム 5種／高保湿バターテクスチャー／べたつかない／すべすべハンドケア／ほのかな香り／アロマ／ナイアシンアミド／ツボクサエキス</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>トーン28</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="b">
+        <v>0</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191891962</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1210333469</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>toun28_official</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>【公式】ボディローション300g／アロママッサージ／背中ニキビ／角質ケア／皮脂・保湿ケア／鎮静／大容量／8種の天然オイル配合</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>トーン28</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1</v>
+      </c>
+      <c r="H227" t="b">
+        <v>0</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210333469</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>1191312885</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>toun28_official</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>【公式】【抹茶セラムSpecialセット】抹茶セラム50ml+ペプタシカセラムパッド 60枚入／低分子ペプチド／弾力ケア／保湿ケア／高純度／角質ケア／肌荒れ防止</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>トーン28</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="b">
+        <v>0</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191312885</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1189243900</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>yomite</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>【公式】body用(3箱セット)【自宅でハーブピーリング】美容施術 韓国化粧品研究機関共同開発</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>on:myskin</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>16146</v>
+      </c>
+      <c r="G229" t="n">
+        <v>7</v>
+      </c>
+      <c r="H229" t="b">
+        <v>0</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189243900</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1189190089</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>yomite</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>【公式】デュアルクリーム毛穴 乾燥 くすみ たるみ ハリ弾力 透明感 保湿 高保湿 水光肌 ツヤ肌 バリア機能 韓国スキンケア 集中ケア エイジングケア　ピーリング　ケア　角質　もっちり</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>on:myskin</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>5980</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="b">
+        <v>0</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189190089</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1056915401</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>bean_products</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>【公式】2個セット スキンケアケアクリーム ビーンバクチオールセラミッククリーム 30g (バクチオール＋CICA＋ナイアシンアミド)日本製 シワ しみ 毛穴開き ツヤ肌 水光肌 陶器肌エイジングケア</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>BEAN</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>9900</v>
+      </c>
+      <c r="G231" t="n">
+        <v>3</v>
+      </c>
+      <c r="H231" t="b">
+        <v>0</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1056915401</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J222"/>
+  <autoFilter ref="A1:J231"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J231"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9926,8 +9926,418 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>1083543606</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>bijin-seizo</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>ザセラム E-XO 80ml 美容液 エクソソーム NMN エイジングケア ユニセックス 保湿美容液 小ジワ くすみ 乾燥 肌荒れ ドクターズコスメ　Dr.ERI</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>イースペシャル</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>13200</v>
+      </c>
+      <c r="G232" t="n">
+        <v>2</v>
+      </c>
+      <c r="H232" t="b">
+        <v>0</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1083543606</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1083543592</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>bijin-seizo</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>マイルドドクターピール 美容液 ピーリング スキンクリアセラム 角質ケア 角質 毛穴 ケア しみ くすみ 乾燥 敏感肌 ドクターズコスメ　Dr.ERI</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>イースペシャル</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>6050</v>
+      </c>
+      <c r="G233" t="n">
+        <v>7</v>
+      </c>
+      <c r="H233" t="b">
+        <v>0</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1083543592</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1083543569</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>bijin-seizo</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>クレンジングジェル 500ml ビッグボトル 大 メイク落とし クレンジング 容量 洗顔 W洗顔不要 毛穴 乾燥 保湿　ドクターズコスメ Dr.ERI</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>イースペシャル</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>14300</v>
+      </c>
+      <c r="G234" t="n">
+        <v>7</v>
+      </c>
+      <c r="H234" t="b">
+        <v>0</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1083543569</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>1083543590</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>bijin-seizo</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>【4本セットで30％OFF】 クレンジングジェル メイク落とし クレンジング 120ml 洗顔 W洗顔不要 保湿 乾燥 敏感肌 ドクターズコスメ　Dr.ERI</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>イースペシャル</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>13860</v>
+      </c>
+      <c r="G235" t="n">
+        <v>2</v>
+      </c>
+      <c r="H235" t="b">
+        <v>0</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1083543590</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1158450594</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>lululun</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>プレミアムルルルン ひんやりマスク</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>ルルルン</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G236" t="n">
+        <v>6</v>
+      </c>
+      <c r="H236" t="b">
+        <v>0</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1158450594</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>1126430151</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>beaund</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>【公式正品】 機能性 ブースタージェル PDRN配合 3点セット</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>BEAUND</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>6100</v>
+      </c>
+      <c r="G237" t="n">
+        <v>2</v>
+      </c>
+      <c r="H237" t="b">
+        <v>0</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1126430151</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1191588853</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>alidadashop</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ピテラ ベスト コレクション トライアル キット 化粧水75mL 美容液10mL クリーム15g スキンケアセット 保湿 透明感 ハリ</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>SK-Ⅱ</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>12649</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="b">
+        <v>0</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191588853</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>1202669462</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>alidadashop</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>ジェノプティクス インフィニットオーラ ジェルクリーム 50g</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>SK-Ⅱ</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>18655</v>
+      </c>
+      <c r="G239" t="n">
+        <v>2</v>
+      </c>
+      <c r="H239" t="b">
+        <v>0</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202669462</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>1198647775</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>alidadashop</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>スキンパワー リニュー クリーム 15g 3個セット 美容クリーム 携帯ミニサイズ 保湿 ハリ ふっくら クリア肌</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>SK-Ⅱ</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>8099</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="b">
+        <v>0</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198647775</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>1206647975</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>doraggunoougoku</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>フィリップス 電動シェーバー 3000Xシリーズ X3051／00 ( 1台 )</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>フィリップス</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="b">
+        <v>0</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206647975</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J231"/>
+  <autoFilter ref="A1:J241"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$255</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J241"/>
+  <dimension ref="A1:J255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10336,8 +10336,582 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1210196616</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>fancylifecosme</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>26年夏数量限定・2個セット メイク キープ ミスト EX + 超COOL 80mL×2個セット レモンミントの香り メイクアップ 仕上げ用ローション</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Kose</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>2750</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="b">
+        <v>0</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210196616</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1160831840</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>fancylifecosme</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>国内正規品 スムージングリファイナー 本体 120ml (ふきとり美容液)</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>リサージ</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="b">
+        <v>0</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1160831840</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1190405436</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>シロル クリスタルホイップ ブラック 120g 洗顔 洗顔後フォーム 泡 保湿 炭酸 炭 毛穴 しろる シロルブラック</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>SHIRORU</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>3798</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="b">
+        <v>0</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190405436</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1166971680</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Sirojam シロジャム ハンドクリーム 医薬部外品 保湿 25g</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>HAN.d</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>4280</v>
+      </c>
+      <c r="G245" t="n">
+        <v>2</v>
+      </c>
+      <c r="H245" t="b">
+        <v>0</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1166971680</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1106411498</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ch2o-ysfactory</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>【国内正規品】 モイスチャー クリーム1 【25ml】</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>エンビロン</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>5280</v>
+      </c>
+      <c r="G246" t="n">
+        <v>4</v>
+      </c>
+      <c r="H246" t="b">
+        <v>0</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1106411498</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1206513959</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ch2o-ysfactory</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SP バン プレバシオン RX 1000ｍl 業務用スカルプシャンプー ポンプ付 業務・詰替用</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>ケラスターゼ</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>11900</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="b">
+        <v>0</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206513959</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>1189789264</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ch2o-ysfactory</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>【外箱にイタミあり】【正規品】 フェイスフルイド 30ml 美容液</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>WiQo</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>11900</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="b">
+        <v>0</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1189789264</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1141183919</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>ch2o-ysfactory</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>【正規品】 DR TAホワイトローションn（医薬部外品） 150mL</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>ナビジョン</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>7490</v>
+      </c>
+      <c r="G249" t="n">
+        <v>4</v>
+      </c>
+      <c r="H249" t="b">
+        <v>0</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1141183919</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1113268244</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>ch2o-ysfactory</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>【国内正規品】 【NEW】 A－ブーストセラム 30ml ブーストセラム</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>エンビロン</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>12980</v>
+      </c>
+      <c r="G250" t="n">
+        <v>4</v>
+      </c>
+      <c r="H250" t="b">
+        <v>0</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1113268244</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>1200999438</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>growthK</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>POLA ポーラ ダイヴ ブライトセラム 100mL 美容液 Dive ダイブ 送料無料 当日発送</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>ブランドなし</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>11620</v>
+      </c>
+      <c r="G251" t="n">
+        <v>3</v>
+      </c>
+      <c r="H251" t="b">
+        <v>0</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200999438</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>1138276433</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>growthK</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>資生堂 ナビジョンDR ウォッシングフォーム しっとり泡タイプ 200ml</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>ナビジョン</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>3730</v>
+      </c>
+      <c r="G252" t="n">
+        <v>5</v>
+      </c>
+      <c r="H252" t="b">
+        <v>0</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1138276433</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1173292080</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>serafinet</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>エンビロン Ｃ-クエンス セラム1 35m l 保湿クリーム ENVIRON</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>エンビロン</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>18550</v>
+      </c>
+      <c r="G253" t="n">
+        <v>3</v>
+      </c>
+      <c r="H253" t="b">
+        <v>0</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1173292080</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1170163946</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>serafinet</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>DRX VCコンセントレート15b 12ml 美容液 ロート製薬</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>ロート製薬</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>5780</v>
+      </c>
+      <c r="G254" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" t="b">
+        <v>0</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1170163946</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1160567733</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>serafinet</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>ナビジョンDR TAホワイトエマルジョンn 120ml 薬用美白乳液 選べる2タイプ</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>ナビジョン</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>9690</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="b">
+        <v>0</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1160567733</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J241"/>
+  <autoFilter ref="A1:J255"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$258</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J255"/>
+  <dimension ref="A1:J258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10910,8 +10910,131 @@
         </is>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>1207691214</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>pricelab</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>NICORIO Lakubi ラクビ プレミアム A 31粒 ( サプリメント 機能性表示食品 )</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>ニコリオ</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>2980</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="b">
+        <v>0</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207691214</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>1207910422</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>pricelab</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>【数量限定価格】FORDAYS フォーデイズ ムーサ イオ DN ジェルクレンジング final 110g クレンジング</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>フォーデイズ</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G257" t="n">
+        <v>1</v>
+      </c>
+      <c r="H257" t="b">
+        <v>0</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207910422</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>1207693501</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>hf-store</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>コー セー メイクキープミスト EX+ クール 2026年発売</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Kose</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="b">
+        <v>0</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207693501</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J255"/>
+  <autoFilter ref="A1:J258"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$258</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$261</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J258"/>
+  <dimension ref="A1:J261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11033,8 +11033,131 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>1202091445</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>beautyokbank</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>プラミー 3-in-1マルチエフェクトグロースプレー75ml(保湿・メイクキープ・水光肌）</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>PRAMY</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>3199</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="b">
+        <v>0</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202091445</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1183583361</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>eternam</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>導入美容液 エテルナム 上清原液 レチノール ナイアシンアミド ビタミンC 集中 ブースター SAITAI セラム 幹細胞 毛穴 スペシャルケア</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Eternam</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="b">
+        <v>0</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1183583361</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>1211284889</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>BLS</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>熊野油脂 馬油シャンプー 詰め替え用 1000ml ＋馬油コンディショナー つめかえ用 1000ml</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>馬油</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>2090</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" t="b">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211284889</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J258"/>
+  <autoFilter ref="A1:J261"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$261</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J261"/>
+  <dimension ref="A1:J267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11156,8 +11156,254 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1133948597</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>blackhobby</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>[1+@ セール] DAEJEON LEMON BREAD 30ml (レモン+マドレーヌ) / 30万個販売突破！韓国で大人気のドレス香水！[533]</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>BLACKHOBBY</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>2690</v>
+      </c>
+      <c r="G262" t="n">
+        <v>3</v>
+      </c>
+      <c r="H262" t="b">
+        <v>0</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1133948597</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1127280603</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>blackhobby</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>[1+@ セール] MILK TEA 30ml (ミルク+コーヒー) / 30万個販売突破！韓国で大人気のドレス香水！[141]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>BLACKHOBBY</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>2690</v>
+      </c>
+      <c r="G263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" t="b">
+        <v>0</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1127280603</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>1185095025</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>neobc</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>【2点セット】タマリス ソルティール ケアマスククリーム ジャスミン 80g</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>タマリス</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>2654</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="b">
+        <v>0</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1185095025</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>1191932541</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>neobc</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>モイストヴェール シャンプー 280ml &amp;amp; トリートメント230g</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>スプリナージュ</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>3643</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="b">
+        <v>0</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191932541</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1185095289</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>neobc</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>【詰替】BCクア フォルムコントロール シャンプー 600ml</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>シュワルツコフ</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>1858</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="b">
+        <v>0</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1185095289</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>1185095139</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>neobc</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>【詰替】BCクア カラースペシフィーク トリートメント 600g</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>シュワルツコフ</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>2542</v>
+      </c>
+      <c r="G267" t="n">
+        <v>2</v>
+      </c>
+      <c r="H267" t="b">
+        <v>0</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1185095139</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J261"/>
+  <autoFilter ref="A1:J267"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$269</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J267"/>
+  <dimension ref="A1:J269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11402,8 +11402,90 @@
         </is>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1194899771</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>yuri775</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>【メーカー生産終了】&amp;amp;honey (アンドハニー)【旧品2023】 ディープ モイスト ハンドクリーム (しっとり) フルールハニーの香り50g ハンドクリーム・ハンドローション</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>アンドハニー</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>1580</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" t="b">
+        <v>0</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194899771</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>1188007931</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>cohabiyo</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>レブロン カラーステイ スウェード インク リップスティック 001 ガット インスティンクト :ベージュピンク(イエベ・ブルべ) 落ちにくい 色移しにくい ふわっとマット 2.55g リップカラー</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>レブロン</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>2254</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="b">
+        <v>0</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188007931</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J267"/>
+  <autoFilter ref="A1:J269"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$277</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J269"/>
+  <dimension ref="A1:J277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11484,8 +11484,336 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>1163564091</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>attation</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>【製薬会社共同開発】ロージーブルーム高濃縮ビタミンアンプル20ml・透明感ケア・うるおう・保湿ケア・肌トーンケア・ツヤ</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>ATTATION</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>2956</v>
+      </c>
+      <c r="G270" t="n">
+        <v>2</v>
+      </c>
+      <c r="H270" t="b">
+        <v>0</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163564091</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>1071677053</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>attation</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>アロマオイル 車用ディフューザー 50ml 天然オイル高配合3種類選択</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>ATTATION</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>2890</v>
+      </c>
+      <c r="G271" t="n">
+        <v>8</v>
+      </c>
+      <c r="H271" t="b">
+        <v>0</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1071677053</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>1212880833</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>sixthsensenagoya</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>【2個セット】プラスリストア UVリタッチスプレー 40g SPF50+　PA++++ 日焼け止め</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>プラスリストア</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>4600</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" t="b">
+        <v>0</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212880833</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1151518249</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>sixthsensenagoya</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>ジャンマリーニ スキンリサーチ　デュアリティー フェイスクリーム</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>ジャンマリニ</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G273" t="n">
+        <v>2</v>
+      </c>
+      <c r="H273" t="b">
+        <v>0</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1151518249</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>967844434</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>helenasgarden</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>医薬部外品 D-bar ディーバー 15ｇ　デオドラント デオドラントクリーム 制汗　ディーシリーズ</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>ケイセイ</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G274" t="n">
+        <v>8</v>
+      </c>
+      <c r="H274" t="b">
+        <v>0</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=967844434</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>1206187502</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>helenasgarden</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>ウルピールフォーム 180g　洗顔料 敏感肌 乾燥肌 グリコール酸 セラミド ピーリング洗顔</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>サンソリット</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>2970</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="b">
+        <v>0</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206187502</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>1199687551</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>helenasgarden</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>ポスト投函 U・Vlock プレミアムブライト 30粒（30日分）【飲む日焼け止め/紫外線対策/サプリメント/ビタミンC/ユーブロック】</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>サンソリット</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>11880</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="b">
+        <v>0</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199687551</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>1206189873</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>helenasgarden</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2本セット ウルピールフォーム 180g　洗顔料 敏感肌 乾燥肌 グリコール酸 セラミド ピーリング洗顔</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>サンソリット</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>5940</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" t="b">
+        <v>0</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206189873</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J269"/>
+  <autoFilter ref="A1:J277"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$277</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$285</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J277"/>
+  <dimension ref="A1:J285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11812,8 +11812,336 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>1184081862</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>lush</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>パワーマスクSP 125g 兼用 スクラブ マスク 毛穴ケア 角質除去 ハチミツ ミント 清涼感 オーガニック 合成保存料不使用 自然派 ギフト</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>LUSH</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>1920</v>
+      </c>
+      <c r="G278" t="n">
+        <v>8</v>
+      </c>
+      <c r="H278" t="b">
+        <v>0</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184081862</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>1191796899</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>brilliant-cosme</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>選べる2種 エヌドット スタイリングフォーム 200g サロン専売 美容室専売 スタイリング ムース N. NAPLA</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>エヌドット</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G279" t="n">
+        <v>2</v>
+      </c>
+      <c r="H279" t="b">
+        <v>0</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191796899</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>1117987309</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>brilliant-cosme</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>【セット販売】 ガルバ CMC ケア シャンプー 400ml + トリートメント 400ml 美容室専売 サロン専売品 GALBA</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>リトルサイエンティスト</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>8700</v>
+      </c>
+      <c r="G280" t="n">
+        <v>1</v>
+      </c>
+      <c r="H280" t="b">
+        <v>0</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1117987309</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>1117987227</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>brilliant-cosme</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>[セット販売] ガルバ CMC ケア シャンプー 400g + トリートメント 400g レフィル 詰め替え 美容室専売 サロン専売品 GALBA</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>リトルサイエンティスト</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>7950</v>
+      </c>
+      <c r="G281" t="n">
+        <v>3</v>
+      </c>
+      <c r="H281" t="b">
+        <v>0</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1117987227</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>1199631740</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>TheBeautyLab</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>オラプレックス No.6 ボンドスムーサー 100ml 流さないトリートメント Olaplex</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>オラプレックス</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>3690</v>
+      </c>
+      <c r="G282" t="n">
+        <v>7</v>
+      </c>
+      <c r="H282" t="b">
+        <v>0</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199631740</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>1199631941</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>TheBeautyLab</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>No.7 ボンディングオイル 30ml オイル トリートメント ヘアオイル スタイリング ブリーチ ダメージケア</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>オラプレックス</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>3470</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" t="b">
+        <v>0</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199631941</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>1199631508</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>TheBeautyLab</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>No.5 ボンドメンテナンス コンディショナー 250ml デイリー トリートメント ブリーチ ダメージケア</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>オラプレックス</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>3490</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="b">
+        <v>0</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199631508</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>1199632284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>TheBeautyLab</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>No.4 ボンドメンテナンス シャンプー 250ml ヘアケア ヘアシャンプ</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>オラプレックス</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>3490</v>
+      </c>
+      <c r="G285" t="n">
+        <v>1</v>
+      </c>
+      <c r="H285" t="b">
+        <v>0</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199632284</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J277"/>
+  <autoFilter ref="A1:J285"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$286</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J285"/>
+  <dimension ref="A1:J286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12140,8 +12140,49 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>1199581644</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>apishmono</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>正規品取扱店 メゾン オルキデ リッチミルク 30ml Maison Orchidee MILK アウトバス ヘアミルク ヘアケア ツヤ 保湿</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Maison Orchidee</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G286" t="n">
+        <v>3</v>
+      </c>
+      <c r="H286" t="b">
+        <v>0</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199581644</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J285"/>
+  <autoFilter ref="A1:J286"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$296</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J286"/>
+  <dimension ref="A1:J296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12181,8 +12181,418 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>1141395563</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>theproduct</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>【公式】ヘアワックス ラベンダー / ヘアバーム オーガニック ワックス スタイリング剤 ヘアオイル サロン品質 保湿 濡れ髪</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>プロダクト</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>2546</v>
+      </c>
+      <c r="G287" t="n">
+        <v>5</v>
+      </c>
+      <c r="H287" t="b">
+        <v>0</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1141395563</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>1199692158</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>lasana</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>ラサーナ プレミオール ホワイトティーの香り 2点セット シャンプー＆トリートメントセット（空ボトル付き）</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>ラサーナ</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>7940</v>
+      </c>
+      <c r="G288" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" t="b">
+        <v>0</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199692158</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>1205854671</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>lasana</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>ラサーナ プレミオール クールリフレッシュ 3点セット（詰め替え用）</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>ラサーナ</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>9820</v>
+      </c>
+      <c r="G289" t="n">
+        <v>1</v>
+      </c>
+      <c r="H289" t="b">
+        <v>0</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205854671</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>1205854660</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>lasana</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>ラサーナ 海藻 ボディソープ 480ml クールタイプ シトラスミントの香り キューブパック（単品）</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>ラサーナ</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>1760</v>
+      </c>
+      <c r="G290" t="n">
+        <v>1</v>
+      </c>
+      <c r="H290" t="b">
+        <v>0</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205854660</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>1159003784</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>iikosui</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>SKALA カール &amp;amp; アフロヘア用 トリートメント 1kg MAIS CRESPOS CREME DE TRATAMENTO ヘアケア ブラジ</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>SKALA</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G291" t="n">
+        <v>1</v>
+      </c>
+      <c r="H291" t="b">
+        <v>0</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1159003784</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>1207662996</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>iikosui</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>ホワイトムスク EDP 40ml SAMOURAI</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>サムライウーマン</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>2803</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" t="b">
+        <v>0</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207662996</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>1207661390</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>iikosui</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>ブルージャスミン EDP 40ml SAMOURAI</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>サムライウーマン</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="b">
+        <v>0</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207661390</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>1001659211</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ADOMANI</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>ブルー ドゥ シャネル オードゥパルファム スプレー CHANEL ショップバッグ付 BLEU DE CHANEL EAU DE PARFUM 50ml SPRAY</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>CHANEL</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>22310</v>
+      </c>
+      <c r="G294" t="n">
+        <v>2</v>
+      </c>
+      <c r="H294" t="b">
+        <v>0</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1001659211</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>1149917566</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>FILLMENT</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>【公式】 [新商品] Qoo10限定クーポン付 オードパフューム misty rain プレミアム香水 フランス香料 韓国コスメ 高級パーピュム</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>FILLMENT</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1</v>
+      </c>
+      <c r="H295" t="b">
+        <v>0</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1149917566</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>1149572944</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>FILLMENT</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>【公式】 [新商品] Qoo10限定クーポン付 オードパフューム sunset teatime プレミアム香水 フランス香料 韓国コスメ 高級パーピュム</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>FILLMENT</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1</v>
+      </c>
+      <c r="H296" t="b">
+        <v>0</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1149572944</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J286"/>
+  <autoFilter ref="A1:J296"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$298</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J296"/>
+  <dimension ref="A1:J298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12591,8 +12591,90 @@
         </is>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>1130451698</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>arth</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>ARTH【自然由来の香料】アース セラピーミスト THERAPY MIST コロン 60ml</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>ARTH</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G297" t="n">
+        <v>2</v>
+      </c>
+      <c r="H297" t="b">
+        <v>0</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1130451698</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>1127506787</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>verre-peri</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>ドレスパフューム 6種 100ML / 香水の代わりに / 高い賦香率/ 服専用香水/ファブリックミスト(除菌・消臭) /芳香剤 消臭剤/フレグランス/韓国コスメ/女性香水 /韓国の人気</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>VERRE PERI</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G298" t="n">
+        <v>3</v>
+      </c>
+      <c r="H298" t="b">
+        <v>0</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1127506787</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J296"/>
+  <autoFilter ref="A1:J298"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$298</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$312</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J298"/>
+  <dimension ref="A1:J312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12673,8 +12673,582 @@
         </is>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>1206310839</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>SHUNZUILIFE</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>UVシルキープロテクション50g SPF50+ PA++++</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>エムディア</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G299" t="n">
+        <v>6</v>
+      </c>
+      <c r="H299" t="b">
+        <v>0</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206310839</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>1205865394</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SHUNZUILIFE</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>UVリタッチスプレー40g　SPF40 PA++++</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>プラスリストア</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0</v>
+      </c>
+      <c r="H300" t="b">
+        <v>0</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205865394</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>1206322437</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>SHUNZUILIFE</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>ホイップウォッシュ200g　エタノールフリー</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>エムディア</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G301" t="n">
+        <v>2</v>
+      </c>
+      <c r="H301" t="b">
+        <v>0</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206322437</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>1206316873</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SHUNZUILIFE</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>スピーディークレンジングジェル　130g</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>エムディア</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>3650</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="b">
+        <v>0</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206316873</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1210570591</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>beautycalendar_japan</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>プラスリストア 洗顔 ピールケア クレンジングソープ泡 ピーリング メイク落とし 角質除去 毛穴 黒ずみ くすみ W洗顔不要 敏感肌 低刺激 スキンケア</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>プラスリストア</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>4100</v>
+      </c>
+      <c r="G303" t="n">
+        <v>1</v>
+      </c>
+      <c r="H303" t="b">
+        <v>0</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210570591</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1210570590</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>beautycalendar_japan</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>プラスリストア 洗顔 クレンジングソープ泡 200ml メイク落とし 洗顔フォーム 泡 W洗顔不要 毛穴ケア 敏感肌 低刺激 スキンケア ホームケア</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>プラスリストア</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" t="b">
+        <v>0</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210570590</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1210570588</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>beautycalendar_japan</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>プラスリストア 洗顔 ホームケア 詰替用 クレンジングソープ泡 レフィル メイク落とし 泡タイプ W洗顔不要 毛穴ケア 敏感肌 低刺激 スキンケア</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>プラスリストア</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>8400</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" t="b">
+        <v>0</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210570588</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>1210570592</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>beautycalendar_japan</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>WiQo（ワイコ）ナリシングクリーム 保湿クリーム 高保湿・乾燥・ハリケア 高い保湿力を持った高機能クリーム</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>WiQo</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>11850</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0</v>
+      </c>
+      <c r="H306" t="b">
+        <v>0</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210570592</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>1063634408</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>beautycalendar_japan</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>【オーガニック韓国香水ブランド】Nichic ニチック 選べる香水の香り 日本初上陸 （30mL）穀物発酵酒精エタノール使用・オーガニック</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Nichic</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" t="b">
+        <v>0</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1063634408</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>1199283765</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>lalashop16</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>プラスリストア クレンジングソープ泡 ホームケア 200ml クレンジング ソープ 洗顔 洗顔料 DAA</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>プラスリストア</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>3650</v>
+      </c>
+      <c r="G308" t="n">
+        <v>7</v>
+      </c>
+      <c r="H308" t="b">
+        <v>0</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199283765</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>1173276573</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>arcmarket</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>1ヶ月たっぷりうるおうプラセンタCゼリー 31本入＋1ヶ月ぷら1ヶ月もっちりうるおうコラーゲンCゼリー 31本</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>アース製薬</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>3240</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" t="b">
+        <v>0</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1173276573</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>1211997200</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>miiplus</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>【Mii+公式】ストレートロックミルク 100g/うねり/ 広がり/クセ毛/熱ケア/トステア/レブリン酸/スタイリング</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Mii+</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>2145</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" t="b">
+        <v>0</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211997200</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1195669932</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>miiplus</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>【単品】ヘアオイル/ヘアミルク/ ダメージケア/うねり/広がり/保湿/スタイリング/サラサラ/ツヤ/洗い流さないトリートメント</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Mii+</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G311" t="n">
+        <v>3</v>
+      </c>
+      <c r="H311" t="b">
+        <v>0</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1195669932</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>1195669775</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>miiplus</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>【選べる2本セット】ヘアオイル/ヘアミルク/ ダメージケア/うねり/広がり/スタイリング/サラサラ/洗い流さないトリートメント</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Mii+</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G312" t="n">
+        <v>5</v>
+      </c>
+      <c r="H312" t="b">
+        <v>0</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1195669775</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J298"/>
+  <autoFilter ref="A1:J312"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$315</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J312"/>
+  <dimension ref="A1:J315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13247,8 +13247,131 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>1141361217</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>aoss</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>TAホワイトセラムMD　薬用TAホフイトロ-ション</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>プラスリストア</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>5470</v>
+      </c>
+      <c r="G313" t="n">
+        <v>5</v>
+      </c>
+      <c r="H313" t="b">
+        <v>0</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1141361217</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>1135197279</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>aoss</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>スピーディークレンジングジェル (クレンジング) 130g</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>エムディア</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>3734</v>
+      </c>
+      <c r="G314" t="n">
+        <v>5</v>
+      </c>
+      <c r="H314" t="b">
+        <v>0</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1135197279</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>1208195301</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>aoss</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>エージー グローイング エッセンス クリーム マスク T</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>ココチ</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>3222</v>
+      </c>
+      <c r="G315" t="n">
+        <v>0</v>
+      </c>
+      <c r="H315" t="b">
+        <v>0</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208195301</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J312"/>
+  <autoFilter ref="A1:J315"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$315</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$328</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J315"/>
+  <dimension ref="A1:J328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13370,8 +13370,541 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>1156302157</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>virginbeautyshop</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>新発売！【日本公式代理店】 ミルクバオバブ CICA ボディウォッシュ ボディローションセット サッパリ 保湿 いい匂い ボディソープ ボディーソープ 清涼</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>ミルクバオバブ</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G316" t="n">
+        <v>1</v>
+      </c>
+      <c r="H316" t="b">
+        <v>0</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1156302157</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>1054859705</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>calatas</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>【公式】サロンバイ トリートメント/350ml/選べる色【Pr/ Pk/ Nv/ Sv/Og】カラーシャンプー/ムラシャン/低刺激/保湿成分/色落ち防止/カラーキープ/美容師/サロン専売</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>カラタス</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>3928</v>
+      </c>
+      <c r="G317" t="n">
+        <v>3</v>
+      </c>
+      <c r="H317" t="b">
+        <v>0</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1054859705</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>1185499227</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>shop-miyabe</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>エヌドット ナチュラルバーム UR 45g</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>ナプラ</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>1947</v>
+      </c>
+      <c r="G318" t="n">
+        <v>17</v>
+      </c>
+      <c r="H318" t="b">
+        <v>0</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1185499227</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>1185499226</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>shop-miyabe</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>エヌドット ポリッシュオイル UR 150ml</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>ナプラ</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>3289</v>
+      </c>
+      <c r="G319" t="n">
+        <v>10</v>
+      </c>
+      <c r="H319" t="b">
+        <v>0</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1185499226</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>1185499176</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>shop-miyabe</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>オージュアグロウシブスカルプマスク 1000g</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>ミルボン</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>11770</v>
+      </c>
+      <c r="G320" t="n">
+        <v>0</v>
+      </c>
+      <c r="H320" t="b">
+        <v>0</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1185499176</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>1141566599</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>k-syoten</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>ジングテカ トラブルセラム 50ml 75ml</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>bring green</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>3790</v>
+      </c>
+      <c r="G321" t="n">
+        <v>2</v>
+      </c>
+      <c r="H321" t="b">
+        <v>0</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1141566599</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>1192655613</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>grabityofficial</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>【公式】 グラビティ シャンプー G0.0 Extra Strong &amp;amp; Strong 475ml</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>grabity</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" t="b">
+        <v>0</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1192655613</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>1185949288</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>kew82417</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>ラビット by ドクタージー ポアスージングクリーム 50ml</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>バイアウア</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G323" t="n">
+        <v>0</v>
+      </c>
+      <c r="H323" t="b">
+        <v>0</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1185949288</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>1201560060</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>danonal</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>ダノナル ショウブ エクソソーム スカルプセラム130ml 薬用成分配合・抜け毛ケア・頭皮鎮静</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>DANONAL</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>3790</v>
+      </c>
+      <c r="G324" t="n">
+        <v>0</v>
+      </c>
+      <c r="H324" t="b">
+        <v>0</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1201560060</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>1209949431</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>droracle_official</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>【鎮静バリア美容液】 センテラバイオームシカアンプル 50ml CICA ゆらぎ肌 敏感肌 水分チャージ ベタつかない バリアケア 鎮静 Centella Biome</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>ドクターオラクル</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>4140</v>
+      </c>
+      <c r="G325" t="n">
+        <v>0</v>
+      </c>
+      <c r="H325" t="b">
+        <v>0</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209949431</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>1206813636</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>droracle_official</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>【鎮静サンセラム】 センテラバイオームスージングサンセラム 日焼け止め 50ml SPF50+ PA++++ CICA UVケア クーリング 紫外線ダメージ 鎮静 Centella Biome</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>ドクターオラクル</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>3680</v>
+      </c>
+      <c r="G326" t="n">
+        <v>1</v>
+      </c>
+      <c r="H326" t="b">
+        <v>0</v>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206813636</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>1206718265</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>donggubat_japan</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>【NEW】【公式】 厄除けパフュームバー 豊かさの豚 パフュームバーセット / お守りプレゼント/ 韓国 香水 プレミアムディフューザー 固形石鹸 / オールインワン / GIF</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Donggubat</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>3880</v>
+      </c>
+      <c r="G327" t="n">
+        <v>0</v>
+      </c>
+      <c r="H327" t="b">
+        <v>0</v>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206718265</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>1202030229</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>donggubat_japan</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>【NEW】【公式】ダレサンアンプル 50ml / ツヤ・うるおい / メイクキープサポート・UVケア/日焼け止め/ / しっとり・ベタつきにくい/ ビタミン・ポリフェノール・ナイアシンアミ</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Donggubat</t>
+        </is>
+      </c>
+      <c r="F328" t="n">
+        <v>4280</v>
+      </c>
+      <c r="G328" t="n">
+        <v>10</v>
+      </c>
+      <c r="H328" t="b">
+        <v>0</v>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202030229</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J315"/>
+  <autoFilter ref="A1:J328"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$350</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J328"/>
+  <dimension ref="A1:J350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13903,8 +13903,910 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>822330209</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>labottach</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>AC-シオールチークニキビパッチ 4回分(8枚入) 頬にきび 肌荒れ 皮脂 集中ケア 鎮静 BHA AHA 韓国コスメ 鎮静ケア 毛穴ケア アクネ トラブル</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Labottach</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G329" t="n">
+        <v>10</v>
+      </c>
+      <c r="H329" t="b">
+        <v>0</v>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=822330209</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>822324798</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>labottach</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>TゾーンAGフォアヘッドしわパッチ 4枚入 額のしわ 眉間のしわ しわ リフトアップ ハリ 保湿 コラーゲン ヒアルロン酸 エイジング 韓国コスメ ラボタッチ</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Labottach</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>963</v>
+      </c>
+      <c r="G330" t="n">
+        <v>12</v>
+      </c>
+      <c r="H330" t="b">
+        <v>0</v>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=822324798</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>1102160848</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>labottach</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>ダークスポットケアパッチ 32枚入 シミ そばかす 色素沈着 ニキビ跡 角層の奥へ 肌になじむ PDRN ナイアシンアミド 保湿 韓国コスメ ラボタッチ</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Labottach</t>
+        </is>
+      </c>
+      <c r="F331" t="n">
+        <v>1940</v>
+      </c>
+      <c r="G331" t="n">
+        <v>4</v>
+      </c>
+      <c r="H331" t="b">
+        <v>0</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1102160848</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>1162963982</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>lowvibe</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>[公式] ハンドクリーム 50ml（028 UNDRESSED / 057 WAKE UP 9 / KHAKI）</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>LOWVIBE</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G332" t="n">
+        <v>14</v>
+      </c>
+      <c r="H332" t="b">
+        <v>0</v>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1162963982</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>1163067127</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>lowvibe</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>[公式] パフューム ハンドクリーム 50ml × 3本（028 UNDRESSED / 057 WAKE UP 9 / KHAKI）</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>LOWVIBE</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>6300</v>
+      </c>
+      <c r="G333" t="n">
+        <v>0</v>
+      </c>
+      <c r="H333" t="b">
+        <v>0</v>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163067127</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>1188301472</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Blast_US_jp</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>【客室乗務員 愛用】ハンドクリーム セット 133ml×2＋75ml＋30ml 保湿・さわやかな使用感</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>カミール</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>2188</v>
+      </c>
+      <c r="G334" t="n">
+        <v>0</v>
+      </c>
+      <c r="H334" t="b">
+        <v>0</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188301472</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>1194211865</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>monclos</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>【公式】ケラチンボンディングヘアパックトリートメント180ml / ダメージヘア / キューティクル層保護 / ヘアケア / 根元ボリュームアップ / 静電気防止 / ハリ・コシアップ / ツヤケア</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>MONCLOS</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G335" t="n">
+        <v>0</v>
+      </c>
+      <c r="H335" t="b">
+        <v>0</v>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194211865</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>1183297800</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>monclos</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>【公式】コンフォート ハンドクリーム 優しい庭 30ml + キーホルダー</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>MONCLOS</t>
+        </is>
+      </c>
+      <c r="F336" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G336" t="n">
+        <v>4</v>
+      </c>
+      <c r="H336" t="b">
+        <v>0</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1183297800</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>1202024454</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>ichistore</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>常盤薬品工業 サナ なめらか本舗 豆乳イソフラボン リンクルアイクリーム N 20g 単品</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>なめらか本舗</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>980</v>
+      </c>
+      <c r="G337" t="n">
+        <v>3</v>
+      </c>
+      <c r="H337" t="b">
+        <v>0</v>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202024454</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>1176002284</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ichistore</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>【新パッケージ】花王 アイロン用 カールローション ホワイトフローラル＆サボンの香り 110ml 単品</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Liese</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G338" t="n">
+        <v>3</v>
+      </c>
+      <c r="H338" t="b">
+        <v>0</v>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1176002284</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>1208038094</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ichistore</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>花王 ビオレ さらさらパウダーシート せっけんの香り 携帯用 10枚 × 5個 セット</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>ビオレ</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G339" t="n">
+        <v>0</v>
+      </c>
+      <c r="H339" t="b">
+        <v>0</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208038094</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>1204546255</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>ichistore</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>花王 melt メルト シャンプー クリーミーメルトフォーム 炭酸パウダー (1g x 12包) x 2個 セット</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>メルト</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>4180</v>
+      </c>
+      <c r="G340" t="n">
+        <v>2</v>
+      </c>
+      <c r="H340" t="b">
+        <v>0</v>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204546255</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>1212723759</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>osdmarket</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>アクアリッチ ウォータリーエッセンス SPF50+ 120g X 2本 日焼け止め 紫外線防御効果</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>ビオレ</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G341" t="n">
+        <v>3</v>
+      </c>
+      <c r="H341" t="b">
+        <v>0</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212723759</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>1210648122</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>osdmarket</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>ビオレu 泡ハンドソープ 詰替え用 2L 2個 大容量</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>ビオレ</t>
+        </is>
+      </c>
+      <c r="F342" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G342" t="n">
+        <v>0</v>
+      </c>
+      <c r="H342" t="b">
+        <v>0</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210648122</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>1194053865</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>MOMOTOMO</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>【10g×4個入】 バブル スパークリング ブースター CICA / HYALON / PROGLOSS</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>VTコスメティックス</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>698</v>
+      </c>
+      <c r="G343" t="n">
+        <v>1</v>
+      </c>
+      <c r="H343" t="b">
+        <v>0</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194053865</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>1194407001</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>MOMOTOMO</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>[1回分] 1アイバックリフト1100ショットリードルパッチ / 目元 弾力 集中ケア ニードルパッチ 改善 韓国直送</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>シャルド</t>
+        </is>
+      </c>
+      <c r="F344" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G344" t="n">
+        <v>1</v>
+      </c>
+      <c r="H344" t="b">
+        <v>0</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194407001</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>1208281470</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>charde</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>【2026年6月新作】グルタチオン振動アイクリーム 20ml / 美顔器 / 目元ケア / くすみがちな目元ケア / トーンアップ改善</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>シャルド</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>3780</v>
+      </c>
+      <c r="G345" t="n">
+        <v>16</v>
+      </c>
+      <c r="H345" t="b">
+        <v>0</v>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208281470</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>1094120054</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>bihibi-jp</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>【日本公式代理店】韓国 アイクリーム レチノコラーゲン低分子300集中クリーム レチノール レチナール 目元たるみ 30代 40代 50代 低分子フィッシュコラーゲン しわ 目尻 ほうれい 人気</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>CKD_GUARANTEED</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G346" t="n">
+        <v>0</v>
+      </c>
+      <c r="H346" t="b">
+        <v>0</v>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1094120054</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>1145826907</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>bihibi-jp</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>【公式】ウォーターフィット サンセラム 日焼け止め 国内発送 シカ センテラ 韓国コスメ 水分 保湿 鎮静 低刺激 UVカット 化粧下地 紫外線</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="F347" t="n">
+        <v>2530</v>
+      </c>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" t="b">
+        <v>0</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1145826907</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>1175765151</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>bihibi-jp</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>【公式】Vita 3 ACE Aurora Toner 化粧水 保湿 ビタミン インナードライ スキンケア 韓国コスメ 水光肌 トーンアップ ニキビ跡ケア 国内発送</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>オーズナリー</t>
+        </is>
+      </c>
+      <c r="F348" t="n">
+        <v>2790</v>
+      </c>
+      <c r="G348" t="n">
+        <v>3</v>
+      </c>
+      <c r="H348" t="b">
+        <v>0</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1175765151</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>1175759418</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>bihibi-jp</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>【公式】 【LDK受賞】 Vita 3 BBC Pudding Cream ビタミン 跡ケア 保湿 高密着 スキンケア ナイトケア スリーピングパック トーンアップ</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>オーズナリー</t>
+        </is>
+      </c>
+      <c r="F349" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G349" t="n">
+        <v>0</v>
+      </c>
+      <c r="H349" t="b">
+        <v>0</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1175759418</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>1174265093</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>bihibi-jp</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>【公式】 プロバイオシカ インテンシブアンプル アンプル 50ml 美容液 鎮静 保湿 バリア ケア スキンケア センテラ ツボクサ　国内発送</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="F350" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G350" t="n">
+        <v>4</v>
+      </c>
+      <c r="H350" t="b">
+        <v>0</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1174265093</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J328"/>
+  <autoFilter ref="A1:J350"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$352</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J350"/>
+  <dimension ref="A1:J352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14805,8 +14805,90 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>1199108255</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>TROIAREUKE</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>【公式】【Qoo10限定セット】選べるH+ カクテルアンプル70ml＋ACSEN オイルカットクレンジング120mlの2点セット 選べる4種 肌悩み別</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>トロイアルケ</t>
+        </is>
+      </c>
+      <c r="F351" t="n">
+        <v>14300</v>
+      </c>
+      <c r="G351" t="n">
+        <v>17</v>
+      </c>
+      <c r="H351" t="b">
+        <v>0</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199108255</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>1164887653</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>TROIAREUKE</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>【公式】ACSEN AC スポットソリューション15ml　高濃度CICA　美容液　肌トラブルケア　肌ダメージケア　肌荒れ　赤み　ツボクサエキス</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>トロイアルケ</t>
+        </is>
+      </c>
+      <c r="F352" t="n">
+        <v>10560</v>
+      </c>
+      <c r="G352" t="n">
+        <v>15</v>
+      </c>
+      <c r="H352" t="b">
+        <v>0</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1164887653</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J350"/>
+  <autoFilter ref="A1:J352"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$352</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$366</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J352"/>
+  <dimension ref="A1:J366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14887,8 +14887,582 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>1206439966</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>purcell</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>【シミくすみケア】80億/mL グルタチオン TXA クリーム</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>PURCELL</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>2970</v>
+      </c>
+      <c r="G353" t="n">
+        <v>4</v>
+      </c>
+      <c r="H353" t="b">
+        <v>0</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206439966</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>1089649902</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>frankly</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>【売上No.1】クローザーセラム60ml【毛穴＆弾力】</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>frankly</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>2960</v>
+      </c>
+      <c r="G354" t="n">
+        <v>12</v>
+      </c>
+      <c r="H354" t="b">
+        <v>0</v>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1089649902</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>1089649517</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>frankly</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>[公式](しっとり 柔らかい)クローザートナーパッド70枚</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>frankly</t>
+        </is>
+      </c>
+      <c r="F355" t="n">
+        <v>2999</v>
+      </c>
+      <c r="G355" t="n">
+        <v>3</v>
+      </c>
+      <c r="H355" t="b">
+        <v>0</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1089649517</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>1141474730</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>badskin23</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>[しっとり水分SET] ヒアルロニックスパトナー 500ml + ヒアルロニックスージングクリーム 100ml</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>BAD SKIN</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>2356</v>
+      </c>
+      <c r="G356" t="n">
+        <v>3</v>
+      </c>
+      <c r="H356" t="b">
+        <v>0</v>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1141474730</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>1141474290</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>badskin23</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>[アンチ リンクルSET] コラーゲンボム ハイドレーティングアンプル 400ml+コラーゲンボム ハイリフティングクリーム 100ml+コラーゲン ボム リジュビネーティング アイクリーム 90ml</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>BAD SKIN</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>3944</v>
+      </c>
+      <c r="G357" t="n">
+        <v>13</v>
+      </c>
+      <c r="H357" t="b">
+        <v>0</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1141474290</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>1077126737</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>badskin23</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>ヒアルロニックスパトナー 500ml / ヒアルロン酸5％配合 / ヌンアム温泉水85％ / 保湿および鎮静効果 / 微酸性化粧水 / 韓国製造</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>BAD SKIN</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>1898</v>
+      </c>
+      <c r="G358" t="n">
+        <v>18</v>
+      </c>
+      <c r="H358" t="b">
+        <v>0</v>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1077126737</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>785767515</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>nakanofactory</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>エルコス（ELLCOS） キュプアスカラーバター 200g 16色から選べる 2本セット トリートメントカラー カラー剤 トリートメント 白髪染め ヘアカラー 低刺激 ヘアケア メール便送料無料</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>エルコス</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>4278</v>
+      </c>
+      <c r="G359" t="n">
+        <v>1</v>
+      </c>
+      <c r="H359" t="b">
+        <v>0</v>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=785767515</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>650971767</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>nakanofactory</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>エルコス Eセラップ PHC 1000g ( 詰替用 リフィル ) ダメージヘアケアトリートメント ペーハーコントロール 業務用 美容室 サロン サロン専売品 送料無料</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>エルコス</t>
+        </is>
+      </c>
+      <c r="F360" t="n">
+        <v>6690</v>
+      </c>
+      <c r="G360" t="n">
+        <v>1</v>
+      </c>
+      <c r="H360" t="b">
+        <v>0</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=650971767</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>1184571774</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>asu</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Lair De SAVON(レールデュサボン) レールデュサボン スパークリングディライト オードトワレ MINI 8mL フレグランス</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>レールデュサボン</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>1516</v>
+      </c>
+      <c r="G361" t="n">
+        <v>0</v>
+      </c>
+      <c r="H361" t="b">
+        <v>0</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>120000022</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184571774</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>1184571772</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>asu</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>キャンメイク アイシャドウベースRB ラディアントブルー 2g</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>キャンメイク</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" t="b">
+        <v>0</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>120000023</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184571772</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1172140378</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>bellefille</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>【セット販売】LADAMER ラダメール セラム 50ml・ピーリング ピンプルパッド 30枚入 箱なし　正規品</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>LADAMER</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>15400</v>
+      </c>
+      <c r="G363" t="n">
+        <v>9</v>
+      </c>
+      <c r="H363" t="b">
+        <v>0</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1172140378</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1177164877</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>bellefille</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>【２本セット】LADAMER ラダメール セラム 50ml 箱なし　正規品</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>LADAMER</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>17600</v>
+      </c>
+      <c r="G364" t="n">
+        <v>1</v>
+      </c>
+      <c r="H364" t="b">
+        <v>0</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1177164877</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1184190269</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>SankyuSankyu</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>PDRN ビタ トーニング アンプル 30ml サーモンPDRN美容液 /肌 エイジングケア</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>ジェナベール</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="b">
+        <v>0</v>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184190269</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1152356637</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>SankyuSankyu</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>シルクペプチドインテンシブリフティングアンプル 35ml!シーズン2![[新しいバージョンでやってきました]]</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Sung Boon Editor</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>4299</v>
+      </c>
+      <c r="G366" t="n">
+        <v>17</v>
+      </c>
+      <c r="H366" t="b">
+        <v>0</v>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1152356637</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J352"/>
+  <autoFilter ref="A1:J366"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$374</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J366"/>
+  <dimension ref="A1:J374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15461,8 +15461,336 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1102212162</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>atomonth</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>オールナチュラル 赤ちゃんこんにゃく スポンジ</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>ATOMONTH</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>600</v>
+      </c>
+      <c r="G367" t="n">
+        <v>0</v>
+      </c>
+      <c r="H367" t="b">
+        <v>0</v>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1102212162</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1208927582</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>konnyaku-shabon</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>数量限定　ミントしゃぼん</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>蒟蒻しゃぼん</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G368" t="n">
+        <v>0</v>
+      </c>
+      <c r="H368" t="b">
+        <v>0</v>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208927582</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>1019090954</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>konnyaku-shabon</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>沖縄 マンゴー / 洗顔石鹸 / セラミド配合 (無添加/キメ整え)</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>蒟蒻しゃぼん</t>
+        </is>
+      </c>
+      <c r="F369" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G369" t="n">
+        <v>0</v>
+      </c>
+      <c r="H369" t="b">
+        <v>0</v>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1019090954</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>884136079</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>konnyaku-shabon</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>京都 柚子 / 洗顔石鹸 / セラミド配合 (無添加/しっとり)</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>蒟蒻しゃぼん</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G370" t="n">
+        <v>1</v>
+      </c>
+      <c r="H370" t="b">
+        <v>0</v>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=884136079</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>1140284862</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>konnyaku-shabon</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>東京ソラマチ限定しゃぼん　粋/ 洗顔石鹸 / セラミド配合 (無添加/肌荒れ)</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>蒟蒻しゃぼん</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G371" t="n">
+        <v>1</v>
+      </c>
+      <c r="H371" t="b">
+        <v>0</v>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1140284862</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>1134625680</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>joseph-japan</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>【正規品】ボディケアセット ボディソープ ＋ ボディローション 低刺激 潤い パフューム ボディケア 各500ml 大容量 男性 女性 誕生日 ギフト プレゼント</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>OPTATUM</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>5280</v>
+      </c>
+      <c r="G372" t="n">
+        <v>4</v>
+      </c>
+      <c r="H372" t="b">
+        <v>0</v>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1134625680</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>1131031359</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>joseph-japan</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>【正規品】ボディローション 大容量 500ml 香水 いい香り しっとり 潤い フルーティー ボディケア ボディクリーム ギフト プレゼント</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>OPTATUM</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>2640</v>
+      </c>
+      <c r="G373" t="n">
+        <v>7</v>
+      </c>
+      <c r="H373" t="b">
+        <v>0</v>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1131031359</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>1089905468</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>joseph-japan</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>【正規品】ボディソープ 500ml 大容量 潤い しっとり 癒しの香り パフューム ボディケア 誕生日 受験生 母の日 ギフト プレゼント</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>OPTATUM</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>2640</v>
+      </c>
+      <c r="G374" t="n">
+        <v>19</v>
+      </c>
+      <c r="H374" t="b">
+        <v>0</v>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1089905468</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J366"/>
+  <autoFilter ref="A1:J374"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$374</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$378</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J374"/>
+  <dimension ref="A1:J378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15789,8 +15789,172 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>1209235049</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>differNdeeper</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>【公式】メラチノール クラウドクリーム 50g /レチノール/メラニンケア/シミケア</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>DIFFER&amp;amp;DEEPER</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G375" t="n">
+        <v>13</v>
+      </c>
+      <c r="H375" t="b">
+        <v>0</v>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209235049</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>1210321053</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>differNdeeper</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>【公式】メラチノール クラウドクリーム 50g＋メラティノールアンプル(2ml*7ea) /レチノール/メラニンケア/シミケア</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>DIFFER&amp;amp;DEEPER</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>5999</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+      <c r="H376" t="b">
+        <v>0</v>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210321053</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>1209234684</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>differNdeeper</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>【公式】ピエルトラ ファーミングバンドリフター 50ml/リフティング/肌のキメ改善/コエンザイム/顔・首のたるみケア /弾力 /シワ・たるみ改善 / 真のVラインケア</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>DIFFER&amp;amp;DEEPER</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>3680</v>
+      </c>
+      <c r="G377" t="n">
+        <v>14</v>
+      </c>
+      <c r="H377" t="b">
+        <v>0</v>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209234684</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>1179474226</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>differNdeeper</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>【公式】【コアリフティングセット】ピエルトラ バンドクリーム30g＋美容液50ml（5種1択）／EGF／セラミド／コラーゲン／保湿ケア／エイジングケア</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>DIFFER&amp;amp;DEEPER</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>5940</v>
+      </c>
+      <c r="G378" t="n">
+        <v>3</v>
+      </c>
+      <c r="H378" t="b">
+        <v>0</v>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179474226</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J374"/>
+  <autoFilter ref="A1:J378"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$378</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$383</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J378"/>
+  <dimension ref="A1:J383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15953,8 +15953,213 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>1085295032</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>hadaha</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>【公式】1+1 ウォーターフル サンエッセンス 本品2個セット/ べースメイク / プライマー効果 / 水分ベース / メイク下地 / UVケア / 高保湿 / 日焼け止め</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>hadaha</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>1580</v>
+      </c>
+      <c r="G379" t="n">
+        <v>17</v>
+      </c>
+      <c r="H379" t="b">
+        <v>0</v>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1085295032</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>1038941140</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>giftman</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>ノット NOTTO ミスト 本体 250ml 国内正規品 マーキュリーコスメティック (sa)</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Mercury Cosmetic</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>2950</v>
+      </c>
+      <c r="G380" t="n">
+        <v>1</v>
+      </c>
+      <c r="H380" t="b">
+        <v>0</v>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1038941140</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>1211104600</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>giftman</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>ストレイン Straine ストレート トリートメント [BASIC] 本体 475mL ホワイトブロッサムの香り さらツヤ 保湿 うるおい (cu3)</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Straine</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>1780</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+      <c r="H381" t="b">
+        <v>0</v>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211104600</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>918994224</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>revinci</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>サクラマチ ヘアファンデーション sakuramachi 白髪隠し 白髪染め ヘアケア ダークブラウ</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>SAKURA MACHI</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G382" t="n">
+        <v>1</v>
+      </c>
+      <c r="H382" t="b">
+        <v>0</v>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=918994224</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>918994136</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>revinci</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>キノラボ　リアロハス　PUA shine　KAI light ハイダメージ　ヘアオイル&amp;amp;セラム スペ</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>K-パレット</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>2035</v>
+      </c>
+      <c r="G383" t="n">
+        <v>4</v>
+      </c>
+      <c r="H383" t="b">
+        <v>0</v>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=918994136</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J378"/>
+  <autoFilter ref="A1:J383"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$383</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$388</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J383"/>
+  <dimension ref="A1:J388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16158,8 +16158,213 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>993021986</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>uebaesou</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>胡粉ネイル　漆黒（しっこく／ブラック／黒）</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>UEBA ESOU</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>1452</v>
+      </c>
+      <c r="G384" t="n">
+        <v>2</v>
+      </c>
+      <c r="H384" t="b">
+        <v>0</v>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=993021986</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>992754452</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>uebaesou</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>胡粉ネイル　スーパーコート（無色透明トップ＆ベースコート）水性ネイル</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>UEBA ESOU</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>1452</v>
+      </c>
+      <c r="G385" t="n">
+        <v>0</v>
+      </c>
+      <c r="H385" t="b">
+        <v>0</v>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=992754452</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>993180450</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>uebaesou</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>胡粉ネイル輝かシリーズ　桃真珠（ももしんじゅ／パールピンク／シアーピンク）</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>UEBA ESOU</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G386" t="n">
+        <v>1</v>
+      </c>
+      <c r="H386" t="b">
+        <v>0</v>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=993180450</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>993042473</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>uebaesou</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>胡粉ネイル　艶紅（つやべに／赤 レッド／マニキュア）</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>UEBA ESOU</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>1452</v>
+      </c>
+      <c r="G387" t="n">
+        <v>1</v>
+      </c>
+      <c r="H387" t="b">
+        <v>0</v>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=993042473</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>993040092</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>uebaesou</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>胡粉ネイル　ミントアイス（ミントグリーン／ペールグリーン／パステルカラー）</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>UEBA ESOU</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>1452</v>
+      </c>
+      <c r="G388" t="n">
+        <v>1</v>
+      </c>
+      <c r="H388" t="b">
+        <v>0</v>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=993040092</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J383"/>
+  <autoFilter ref="A1:J388"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$388</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$390</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J388"/>
+  <dimension ref="A1:J390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16363,8 +16363,90 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>1165124077</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>kyomiori</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>[公式]　星影ながし ： 四季彩まといネイル / 水性ネイル</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>kyo･miori</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G389" t="n">
+        <v>2</v>
+      </c>
+      <c r="H389" t="b">
+        <v>0</v>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1165124077</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>969576330</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>bbmjapan</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>カラーチェンジネイル C-07　SKY BLUE/PURPLE マニキュア ポリッシュ 色が変わる</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>ROYAL BEACH</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>990</v>
+      </c>
+      <c r="G390" t="n">
+        <v>3</v>
+      </c>
+      <c r="H390" t="b">
+        <v>0</v>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>120000021</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=969576330</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J388"/>
+  <autoFilter ref="A1:J390"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$391</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J390"/>
+  <dimension ref="A1:J391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16445,8 +16445,49 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>1118239487</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>kmyfriend</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>ティーツリー エッセンシャルマスク 10枚 + Rococell マスクパック 1枚gift / 肌鎮静 / フェイスパック / 敏感肌 / 保湿化粧品 / 乾燥肌 / 混合性肌 / 韓国パック</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>メディヒール</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>999</v>
+      </c>
+      <c r="G391" t="n">
+        <v>5</v>
+      </c>
+      <c r="H391" t="b">
+        <v>0</v>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1118239487</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J390"/>
+  <autoFilter ref="A1:J391"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$391</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$393</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J391"/>
+  <dimension ref="A1:J393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16486,8 +16486,90 @@
         </is>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>1198759048</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>novelhero</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>ホワイトライスエッセンスマスク 5個セット</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>ピュレア</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>2980</v>
+      </c>
+      <c r="G392" t="n">
+        <v>4</v>
+      </c>
+      <c r="H392" t="b">
+        <v>0</v>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198759048</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>1148801765</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>novelhero</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>CHOIマスク 薬用ニキビケア 5個セット</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>肌美精</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>3670</v>
+      </c>
+      <c r="G393" t="n">
+        <v>17</v>
+      </c>
+      <c r="H393" t="b">
+        <v>0</v>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1148801765</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J391"/>
+  <autoFilter ref="A1:J393"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$393</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$395</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J393"/>
+  <dimension ref="A1:J395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16568,8 +16568,90 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>855165267</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>momoskin</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>(10枚)カラーシナジーエフェクトシートマスク 20 g (韓国コスメ)</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>ディオプラス</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>1630</v>
+      </c>
+      <c r="G394" t="n">
+        <v>0</v>
+      </c>
+      <c r="H394" t="b">
+        <v>0</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=855165267</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>823022187</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>momoskin</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>UVディフェンス日焼け止めクリーム 50 g (韓国コスメ) SPF50+ PA+++</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>ディオプラス</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G395" t="n">
+        <v>3</v>
+      </c>
+      <c r="H395" t="b">
+        <v>0</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=823022187</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J393"/>
+  <autoFilter ref="A1:J395"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$395</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$399</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J395"/>
+  <dimension ref="A1:J399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16650,8 +16650,172 @@
         </is>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>1203571495</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>MABUP</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>【魔法女神公式】レチナールショット タイトニングブースター 20g PDRN スピキュール 針美容液 ハリ 毛穴ケア</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>MABUP YEOSHIN</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>1550</v>
+      </c>
+      <c r="G396" t="n">
+        <v>0</v>
+      </c>
+      <c r="H396" t="b">
+        <v>0</v>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203571495</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>1209763340</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>MABUP</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>【魔法女神公式】1+1 PDRN エクソソーム バブルローション 100ml 泡化粧水 保湿 ハリ 毛穴ケア エイジングケア 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>MABUP YEOSHIN</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>3330</v>
+      </c>
+      <c r="G397" t="n">
+        <v>0</v>
+      </c>
+      <c r="H397" t="b">
+        <v>0</v>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209763340</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>1208516427</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>MABUP</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>【魔法女神公式】1+1 レチナールショット タイトニングブースター 20g PDRN スピキュール 針美容液 ハリ 毛穴ケア</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>MABUP YEOSHIN</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>2403</v>
+      </c>
+      <c r="G398" t="n">
+        <v>5</v>
+      </c>
+      <c r="H398" t="b">
+        <v>0</v>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208516427</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>1204209279</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>MABUP</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>【魔法女神公式】TXA ナイアシンアミド マスク 20枚入り 大容量 シートマスク 保湿 韓国コスメ</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>MABUP YEOSHIN</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+      <c r="H399" t="b">
+        <v>0</v>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204209279</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J395"/>
+  <autoFilter ref="A1:J399"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$399</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$404</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J399"/>
+  <dimension ref="A1:J404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16814,8 +16814,213 @@
         </is>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>1104769890</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>KBOOSTER</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>インテンスブライトWブースターアンプル 30ml</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>K BOOSTER</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>13800</v>
+      </c>
+      <c r="G400" t="n">
+        <v>4</v>
+      </c>
+      <c r="H400" t="b">
+        <v>0</v>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1104769890</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>1165001254</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>KBOOSTER</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>デイリーダーマカプセルサンセラム 50ml</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>K BOOSTER</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G401" t="n">
+        <v>6</v>
+      </c>
+      <c r="H401" t="b">
+        <v>0</v>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1165001254</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>1157754594</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>KBOOSTER</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>デイリーダーマリペアエッセンス 50ml</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>K BOOSTER</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>10440</v>
+      </c>
+      <c r="G402" t="n">
+        <v>4</v>
+      </c>
+      <c r="H402" t="b">
+        <v>0</v>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1157754594</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>1010446828</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>hadamaru</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>公式 クレンジング メイク落とし 140ｇ2本セット / 敏感肌 / 肌荒れ / ニキビ / 低刺激 毛穴 / 黒ずみ / 皮脂 / まつエク / お風呂場 OK</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>はだまる</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>5940</v>
+      </c>
+      <c r="G403" t="n">
+        <v>13</v>
+      </c>
+      <c r="H403" t="b">
+        <v>0</v>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1010446828</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>778876716</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>hadamaru</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>【公式】 乾燥 肌荒れ する肌へ 高保湿 オールインワンゲル 専用ポンプセット ( 敏感肌 / 肌荒れ / 低刺激 /基礎化粧品 ) ヒト型 セラミド 美肌菌 乳酸菌 乾</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>はだまる</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>8580</v>
+      </c>
+      <c r="G404" t="n">
+        <v>11</v>
+      </c>
+      <c r="H404" t="b">
+        <v>0</v>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=778876716</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J399"/>
+  <autoFilter ref="A1:J404"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$404</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$406</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J404"/>
+  <dimension ref="A1:J406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17019,8 +17019,90 @@
         </is>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>1005392041</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>BRIANONLINESTORE</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>3本セット スキャルプトナー 180g 頭皮用化粧水</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>NASEED</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>8970</v>
+      </c>
+      <c r="G405" t="n">
+        <v>0</v>
+      </c>
+      <c r="H405" t="b">
+        <v>0</v>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1005392041</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>962550550</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>BRIANONLINESTORE</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>スキャルプトナー 180g 頭皮用化粧水</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>NASEED</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>2990</v>
+      </c>
+      <c r="G406" t="n">
+        <v>6</v>
+      </c>
+      <c r="H406" t="b">
+        <v>0</v>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=962550550</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J404"/>
+  <autoFilter ref="A1:J406"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$406</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$411</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J406"/>
+  <dimension ref="A1:J411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17101,8 +17101,213 @@
         </is>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>1167784807</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>beigicofficial</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>ボタニカルリカバリーカフェインシャンプー</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>ベージック</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>4300</v>
+      </c>
+      <c r="G407" t="n">
+        <v>2</v>
+      </c>
+      <c r="H407" t="b">
+        <v>0</v>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1167784807</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>1153077693</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>beigicofficial</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>ルミナスハイドレーティングシートマスク 4枚入り箱</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>ベージック</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G408" t="n">
+        <v>4</v>
+      </c>
+      <c r="H408" t="b">
+        <v>0</v>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1153077693</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>1199374983</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>beigicofficial</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>【NEW】ビタミンCアクティブカプセル 4箱(24カプセル) + トリートメントエッセンス120ml 1つ</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>ベージック</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>22750</v>
+      </c>
+      <c r="G409" t="n">
+        <v>0</v>
+      </c>
+      <c r="H409" t="b">
+        <v>0</v>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199374983</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>1184116639</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>beigicofficial</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>クラシックネイル＆ハンドクリーム BS</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>ベージック</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G410" t="n">
+        <v>2</v>
+      </c>
+      <c r="H410" t="b">
+        <v>0</v>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1184116639</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>1180515682</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>beigicofficial</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>エンハンスドファーミングクリーム 50ml</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>ベージック</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>8900</v>
+      </c>
+      <c r="G411" t="n">
+        <v>5</v>
+      </c>
+      <c r="H411" t="b">
+        <v>0</v>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180515682</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J406"/>
+  <autoFilter ref="A1:J411"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$411</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$413</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J411"/>
+  <dimension ref="A1:J413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17306,8 +17306,90 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>1199145866</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>dudududu</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>ゴールドスネイルモイスチャライジングマスク（25ml×10ea）</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>SUNSKIN</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G412" t="n">
+        <v>0</v>
+      </c>
+      <c r="H412" t="b">
+        <v>0</v>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199145866</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>1158333234</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>meiyeshengwu</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>【2箱セット】保湿ケアマスク28ml*5枚</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>PROF.LING</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G413" t="n">
+        <v>0</v>
+      </c>
+      <c r="H413" t="b">
+        <v>0</v>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1158333234</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J411"/>
+  <autoFilter ref="A1:J413"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$413</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$414</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J413"/>
+  <dimension ref="A1:J414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17388,8 +17388,49 @@
         </is>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>1171219158</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>aknir</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>AKNIR アクニー 梨花開発 薬用シャンプー トリートメント 詰め替えセット アミノ酸 頭皮ケア 保湿 くせ毛 ト ダメージ補修</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>AKNIR</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>9020</v>
+      </c>
+      <c r="G414" t="n">
+        <v>0</v>
+      </c>
+      <c r="H414" t="b">
+        <v>0</v>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1171219158</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J413"/>
+  <autoFilter ref="A1:J414"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$414</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$420</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J414"/>
+  <dimension ref="A1:J420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17429,8 +17429,254 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>1208418385</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>pouch24</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>POUCH 24 CCC PINK</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>POUCH24</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>2880</v>
+      </c>
+      <c r="G415" t="n">
+        <v>0</v>
+      </c>
+      <c r="H415" t="b">
+        <v>0</v>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208418385</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>1204359387</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>pouch24</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>POUCH 24 ハ・ジウォン スターターセット（クイーンズバーム 16g＋エッセンス 120mL）</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>POUCH24</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>10875</v>
+      </c>
+      <c r="G416" t="n">
+        <v>0</v>
+      </c>
+      <c r="H416" t="b">
+        <v>0</v>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204359387</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>1204229455</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>pouch24</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>メルト＆モイスチャー セット</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>POUCH24</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>9375</v>
+      </c>
+      <c r="G417" t="n">
+        <v>0</v>
+      </c>
+      <c r="H417" t="b">
+        <v>0</v>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204229455</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>1203965108</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>pouch24</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>モルトン シュガースクラブ</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>POUCH24</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>4845</v>
+      </c>
+      <c r="G418" t="n">
+        <v>0</v>
+      </c>
+      <c r="H418" t="b">
+        <v>0</v>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203965108</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>1204220389</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>pouch24</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>シュガー＆バター セット</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>POUCH24</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>7575</v>
+      </c>
+      <c r="G419" t="n">
+        <v>0</v>
+      </c>
+      <c r="H419" t="b">
+        <v>0</v>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204220389</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>1202200235</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>epleme</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>T+S+C (イプレミー) ハイドラセル 3種セット (トナー＋セラム＋クリーム)</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>eple:me</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G420" t="n">
+        <v>0</v>
+      </c>
+      <c r="H420" t="b">
+        <v>0</v>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202200235</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J414"/>
+  <autoFilter ref="A1:J420"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$420</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$421</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J420"/>
+  <dimension ref="A1:J421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17675,8 +17675,49 @@
         </is>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>1198046011</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>WabiSabiShop</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>アイリス ブルーブラック 染毛剤 クリーム ノンブリーチ 流行色 色白見え 植物性 自宅で簡単 染毛 ブルーグレー ブラックパープル 女性 純</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>アイリス</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>926</v>
+      </c>
+      <c r="G421" t="n">
+        <v>0</v>
+      </c>
+      <c r="H421" t="b">
+        <v>0</v>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198046011</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J420"/>
+  <autoFilter ref="A1:J421"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$421</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$424</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J421"/>
+  <dimension ref="A1:J424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17716,8 +17716,131 @@
         </is>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>1179914561</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>uptofficial</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>【公式】安達祐実プロデュースコスメ [Upt(ウプト)] クレンジングバーム_乾燥肌 / クレンジング / 洗顔</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Upt</t>
+        </is>
+      </c>
+      <c r="F422" t="n">
+        <v>2750</v>
+      </c>
+      <c r="G422" t="n">
+        <v>1</v>
+      </c>
+      <c r="H422" t="b">
+        <v>0</v>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179914561</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>1179916284</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>uptofficial</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>【公式】安達祐実プロデュースコスメ [Upt(ウプト)] マイルドピールエッセンス_乾燥肌 / スキンケア / 美容液</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Upt</t>
+        </is>
+      </c>
+      <c r="F423" t="n">
+        <v>2530</v>
+      </c>
+      <c r="G423" t="n">
+        <v>2</v>
+      </c>
+      <c r="H423" t="b">
+        <v>0</v>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179916284</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>1179915130</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>uptofficial</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>【公式】安達祐実プロデュースコスメ [Upt(ウプト)] クリーミーホイップウォッシュ_乾燥肌 / クレンジング / 洗顔</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Upt</t>
+        </is>
+      </c>
+      <c r="F424" t="n">
+        <v>2530</v>
+      </c>
+      <c r="G424" t="n">
+        <v>0</v>
+      </c>
+      <c r="H424" t="b">
+        <v>0</v>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179915130</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J421"/>
+  <autoFilter ref="A1:J424"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$424</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$428</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J424"/>
+  <dimension ref="A1:J428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17839,8 +17839,172 @@
         </is>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>1107189934</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>DEAROHNEUL</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>【2点セット】 DEAR OHNEUL 特許成分 DKMEX エリクサー ドンキークリーム 韓国コスメ保湿クリーム 50ml x 2 超低分子コラーゲン &amp;amp; ロバミルク 保湿/抗炎/抗酸化</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Dear Ohneul</t>
+        </is>
+      </c>
+      <c r="F425" t="n">
+        <v>7700</v>
+      </c>
+      <c r="G425" t="n">
+        <v>0</v>
+      </c>
+      <c r="H425" t="b">
+        <v>0</v>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1107189934</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>1206166293</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>SUMMERHOLIC</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>【本品+リフィル】ウルトラスポーツサンクッション15g本品+サンクッション15gリフィルUVセットSPF50+ PA++++ 日焼け止め UVケア耐水・汗対応 UVケア ヴィーガン処方</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>SUMMER HOLIC</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>4118</v>
+      </c>
+      <c r="G426" t="n">
+        <v>1</v>
+      </c>
+      <c r="H426" t="b">
+        <v>0</v>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206166293</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>1204964891</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>SUMMERHOLIC</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>【2点セット】ウルトラスポーツサンクリーム50ml＋ウルトラスポーツサンスティック19g　UVセットSPF50+ PA++++ 日焼け止め UVケア耐水・汗対応 UVケア ヴィーガン処方</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>SUMMER HOLIC</t>
+        </is>
+      </c>
+      <c r="F427" t="n">
+        <v>4028</v>
+      </c>
+      <c r="G427" t="n">
+        <v>3</v>
+      </c>
+      <c r="H427" t="b">
+        <v>0</v>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204964891</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>1196366848</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>SUMMERHOLIC</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>ウルトラスポーツサンクリーム 200ml 大容量日焼け止め</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>SUMMER HOLIC</t>
+        </is>
+      </c>
+      <c r="F428" t="n">
+        <v>6128</v>
+      </c>
+      <c r="G428" t="n">
+        <v>2</v>
+      </c>
+      <c r="H428" t="b">
+        <v>0</v>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>120000017</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1196366848</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J424"/>
+  <autoFilter ref="A1:J428"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$428</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$429</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J428"/>
+  <dimension ref="A1:J429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18003,8 +18003,49 @@
         </is>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>1112773913</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>aurorazakka</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>シカレチA エッセンス0.3 30ml</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>VTコスメティックス</t>
+        </is>
+      </c>
+      <c r="F429" t="n">
+        <v>2991</v>
+      </c>
+      <c r="G429" t="n">
+        <v>4</v>
+      </c>
+      <c r="H429" t="b">
+        <v>0</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1112773913</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J428"/>
+  <autoFilter ref="A1:J429"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$429</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$430</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J429"/>
+  <dimension ref="A1:J430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18044,8 +18044,49 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>1163342452</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>anoeticbeauty</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>[ダビンPICK]アノエティック シルク パフューム ヘア美容液</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>ANOETIC</t>
+        </is>
+      </c>
+      <c r="F430" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G430" t="n">
+        <v>2</v>
+      </c>
+      <c r="H430" t="b">
+        <v>0</v>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163342452</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J429"/>
+  <autoFilter ref="A1:J430"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$430</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$433</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J430"/>
+  <dimension ref="A1:J433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18085,8 +18085,131 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>1013414380</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>yoshikiyoshi</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>花王Curel（キュレル） 皮脂トラブルケア ミニセット 花王　敏感肌　トライアル</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>キュレル</t>
+        </is>
+      </c>
+      <c r="F431" t="n">
+        <v>1183</v>
+      </c>
+      <c r="G431" t="n">
+        <v>1</v>
+      </c>
+      <c r="H431" t="b">
+        <v>0</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>120000018</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1013414380</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>1052725355</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>yoshikiyoshi</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>ES-L650DK ラムダッシュPRO 6枚刃 シェーバー</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>パナソニック</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>50340</v>
+      </c>
+      <c r="G432" t="n">
+        <v>5</v>
+      </c>
+      <c r="H432" t="b">
+        <v>0</v>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1052725355</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>1013414403</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>yoshikiyoshi</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>松山油脂肌をうるおす保湿スキンケア保湿クレンジング</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>肌をうるおす保湿スキンケア</t>
+        </is>
+      </c>
+      <c r="F433" t="n">
+        <v>1485</v>
+      </c>
+      <c r="G433" t="n">
+        <v>4</v>
+      </c>
+      <c r="H433" t="b">
+        <v>0</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1013414403</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J430"/>
+  <autoFilter ref="A1:J433"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$433</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$437</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J433"/>
+  <dimension ref="A1:J437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18208,8 +18208,172 @@
         </is>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>1159849024</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>skym-store</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>ヴァリジョア シャンプー 300ml + トリートメント 230g セット サロン専売品</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>ディアテック</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>3480</v>
+      </c>
+      <c r="G434" t="n">
+        <v>11</v>
+      </c>
+      <c r="H434" t="b">
+        <v>0</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1159849024</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>1175522511</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>skym-store</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>スカルプブラシ ワールドプレミアム ロング ゴールド 頭皮ケア</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>エス・ハート・エス</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G435" t="n">
+        <v>2</v>
+      </c>
+      <c r="H435" t="b">
+        <v>0</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1175522511</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>1164523402</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>skym-store</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>【3袋セット】 Varijoie ヴァリジョア シャンプー 10ml + トリートメント 10g セット サシェ サロン専売品 お試し トライアル トラベル</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>ディアテック</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>900</v>
+      </c>
+      <c r="G436" t="n">
+        <v>1</v>
+      </c>
+      <c r="H436" t="b">
+        <v>0</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1164523402</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>1161363897</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>skym-store</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>ビーエックス mm ミリ ワックスフォーム 180g スタイリング ウェーブ キープ パーマ シトラスフローラルの香り b-ex 正規品 サロン専売品</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>モルトベーネ</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" t="b">
+        <v>0</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1161363897</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J433"/>
+  <autoFilter ref="A1:J437"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$437</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$438</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J437"/>
+  <dimension ref="A1:J438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18372,8 +18372,49 @@
         </is>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>1208156404</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Donghaeya1007</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>PDRN シカ マスクパック サーモン 保湿 鎮静 ヒアルロン酸 敏感肌用 （10枚入り × 1個）</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>MECIEL</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>5220</v>
+      </c>
+      <c r="G438" t="n">
+        <v>0</v>
+      </c>
+      <c r="H438" t="b">
+        <v>0</v>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1208156404</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J437"/>
+  <autoFilter ref="A1:J438"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$439</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J438"/>
+  <dimension ref="A1:J439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18413,8 +18413,49 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>1213189105</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>michirushop</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>小川生薬 国産くろもじ茶 4g ×12袋 TP クロモジ茶 黒文字茶 ティーバッグ ノンカフェイン 2袋セット</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>小川生薬</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G439" t="n">
+        <v>0</v>
+      </c>
+      <c r="H439" t="b">
+        <v>0</v>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>120000020</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213189105</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J438"/>
+  <autoFilter ref="A1:J439"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/discovery_result_11.xlsx
+++ b/output/discovery_result_11.xlsx
@@ -10,7 +10,7 @@
     <sheet name="저리뷰상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$439</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'저리뷰상품'!$A$1:$J$440</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J439"/>
+  <dimension ref="A1:J440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18454,8 +18454,49 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>963806129</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>themakeshop</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>SELLA クラシック ナチュラル クレンジングバー100g</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>セラ</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G440" t="n">
+        <v>6</v>
+      </c>
+      <c r="H440" t="b">
+        <v>0</v>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>120000012</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=963806129</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J439"/>
+  <autoFilter ref="A1:J440"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>